--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1591,6 +1591,3531 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122232402</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562786</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040064</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122234194</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563154</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040221</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122233217</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562922</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7040240</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122234000</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563097</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040210</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122232949</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562836</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040209</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122232932</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82426</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562795</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7040090</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122233127</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79720</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562875</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7040276</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122233646</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79721</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562989</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7040172</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122232184</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562833</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7040085</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122232495</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79720</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>562748</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7040046</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122233994</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>563088</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7040175</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122232285</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79720</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562818</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7040065</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122233260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562896</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7040281</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122234283</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>563202</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7040231</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122233673</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79756</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562986</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7040156</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122234125</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>563092</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7040220</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122233997</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>563095</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7040157</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122233750</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>563040</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7040180</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122233933</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>563089</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7040225</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122233625</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79720</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562978</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7040170</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122234052</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>563109</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7040194</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122234359</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82426</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>563205</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7040240</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122233350</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>562930</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7040221</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122233345</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562904</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7040280</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122233647</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562988</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7040196</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122232469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90754</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562748</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7040047</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122234103</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>563089</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7040216</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122234058</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>563095</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7040206</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122232270</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79720</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562828</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7040062</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122234038</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>563099</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7040205</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122234176</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>563102</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7040234</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122232402</v>
+        <v>122234194</v>
       </c>
       <c r="B11" t="n">
-        <v>57369</v>
+        <v>78639</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,45 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562786</v>
+        <v>563154</v>
       </c>
       <c r="R11" t="n">
-        <v>7040064</v>
+        <v>7040221</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,14 +1666,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234194</v>
+        <v>122232402</v>
       </c>
       <c r="B12" t="n">
-        <v>78639</v>
+        <v>57369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,37 +1721,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563154</v>
+        <v>562786</v>
       </c>
       <c r="R12" t="n">
-        <v>7040221</v>
+        <v>7040064</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,19 +1786,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1808,22 +1808,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233217</v>
+        <v>122234000</v>
       </c>
       <c r="B13" t="n">
-        <v>78639</v>
+        <v>57369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,34 +1836,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562922</v>
+        <v>563097</v>
       </c>
       <c r="R13" t="n">
-        <v>7040240</v>
+        <v>7040210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1905,7 +1910,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,22 +1930,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122234000</v>
+        <v>122233217</v>
       </c>
       <c r="B14" t="n">
-        <v>57369</v>
+        <v>78639</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,39 +1958,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563097</v>
+        <v>562922</v>
       </c>
       <c r="R14" t="n">
-        <v>7040210</v>
+        <v>7040240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,7 +2017,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2022,12 +2027,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,12 +2042,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234283</v>
+        <v>122233673</v>
       </c>
       <c r="B24" t="n">
-        <v>57369</v>
+        <v>79756</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,46 +3044,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563202</v>
+        <v>562986</v>
       </c>
       <c r="R24" t="n">
-        <v>7040231</v>
+        <v>7040156</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3110,24 +3105,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,22 +3122,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233673</v>
+        <v>122234283</v>
       </c>
       <c r="B25" t="n">
-        <v>79756</v>
+        <v>57369</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,41 +3146,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562986</v>
+        <v>563202</v>
       </c>
       <c r="R25" t="n">
-        <v>7040156</v>
+        <v>7040231</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3227,9 +3212,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,12 +3244,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233350</v>
+        <v>122233647</v>
       </c>
       <c r="B33" t="n">
         <v>57369</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562930</v>
+        <v>562988</v>
       </c>
       <c r="R33" t="n">
-        <v>7040221</v>
+        <v>7040196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233345</v>
+        <v>122233350</v>
       </c>
       <c r="B34" t="n">
         <v>57369</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562904</v>
+        <v>562930</v>
       </c>
       <c r="R34" t="n">
-        <v>7040280</v>
+        <v>7040221</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,19 +4292,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233647</v>
+        <v>122233345</v>
       </c>
       <c r="B35" t="n">
         <v>57369</v>
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562988</v>
+        <v>562904</v>
       </c>
       <c r="R35" t="n">
-        <v>7040196</v>
+        <v>7040280</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4414,12 +4414,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5116,6 +5116,127 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122233875</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79586</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>388</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>563056</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7040119</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234194</v>
+        <v>122234359</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>82430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563154</v>
+        <v>563205</v>
       </c>
       <c r="R11" t="n">
-        <v>7040221</v>
+        <v>7040240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122232402</v>
+        <v>122233673</v>
       </c>
       <c r="B12" t="n">
-        <v>57369</v>
+        <v>79760</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,46 +1717,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562786</v>
+        <v>562986</v>
       </c>
       <c r="R12" t="n">
-        <v>7040064</v>
+        <v>7040156</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1789,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234000</v>
+        <v>122233647</v>
       </c>
       <c r="B13" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,14 +1848,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563097</v>
+        <v>562988</v>
       </c>
       <c r="R13" t="n">
-        <v>7040210</v>
+        <v>7040196</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1910,12 +1897,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233217</v>
+        <v>122232469</v>
       </c>
       <c r="B14" t="n">
-        <v>78639</v>
+        <v>90761</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,13 +1969,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562922</v>
+        <v>562748</v>
       </c>
       <c r="R14" t="n">
-        <v>7040240</v>
+        <v>7040047</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,19 +2002,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122232949</v>
+        <v>122232402</v>
       </c>
       <c r="B15" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,24 +2065,27 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562836</v>
+        <v>562786</v>
       </c>
       <c r="R15" t="n">
-        <v>7040209</v>
+        <v>7040064</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,24 +2112,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,22 +2134,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122232932</v>
+        <v>122234194</v>
       </c>
       <c r="B16" t="n">
-        <v>82426</v>
+        <v>78643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,37 +2162,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562795</v>
+        <v>563154</v>
       </c>
       <c r="R16" t="n">
-        <v>7040090</v>
+        <v>7040221</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2249,9 +2219,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,22 +2246,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233127</v>
+        <v>122234176</v>
       </c>
       <c r="B17" t="n">
-        <v>79720</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,34 +2274,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562875</v>
+        <v>563102</v>
       </c>
       <c r="R17" t="n">
-        <v>7040276</v>
+        <v>7040234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2363,7 +2348,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233646</v>
+        <v>122232932</v>
       </c>
       <c r="B18" t="n">
-        <v>79721</v>
+        <v>82430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562989</v>
+        <v>562795</v>
       </c>
       <c r="R18" t="n">
-        <v>7040172</v>
+        <v>7040090</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122232184</v>
+        <v>122233997</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562833</v>
+        <v>563095</v>
       </c>
       <c r="R19" t="n">
-        <v>7040085</v>
+        <v>7040157</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232495</v>
+        <v>122234103</v>
       </c>
       <c r="B20" t="n">
-        <v>79720</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,37 +2600,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562748</v>
+        <v>563089</v>
       </c>
       <c r="R20" t="n">
-        <v>7040046</v>
+        <v>7040216</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2667,9 +2662,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,12 +2694,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2699,7 +2709,7 @@
         <v>122233994</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2808,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232285</v>
+        <v>122233217</v>
       </c>
       <c r="B22" t="n">
-        <v>79720</v>
+        <v>78643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2824,21 +2834,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,13 +2858,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562818</v>
+        <v>562922</v>
       </c>
       <c r="R22" t="n">
-        <v>7040065</v>
+        <v>7040240</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2881,9 +2891,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,22 +2918,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233260</v>
+        <v>122233127</v>
       </c>
       <c r="B23" t="n">
-        <v>57369</v>
+        <v>79724</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,39 +2946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562896</v>
+        <v>562875</v>
       </c>
       <c r="R23" t="n">
-        <v>7040281</v>
+        <v>7040276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +3005,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,12 +3015,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233673</v>
+        <v>122232495</v>
       </c>
       <c r="B24" t="n">
-        <v>79756</v>
+        <v>79724</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3054,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562986</v>
+        <v>562748</v>
       </c>
       <c r="R24" t="n">
-        <v>7040156</v>
+        <v>7040046</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3134,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122234283</v>
+        <v>122232270</v>
       </c>
       <c r="B25" t="n">
-        <v>57369</v>
+        <v>79724</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,42 +3160,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563202</v>
+        <v>562828</v>
       </c>
       <c r="R25" t="n">
-        <v>7040231</v>
+        <v>7040062</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3212,24 +3217,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,22 +3234,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234125</v>
+        <v>122232184</v>
       </c>
       <c r="B26" t="n">
-        <v>57369</v>
+        <v>78643</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3272,42 +3262,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563092</v>
+        <v>562833</v>
       </c>
       <c r="R26" t="n">
-        <v>7040220</v>
+        <v>7040085</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3334,24 +3319,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233997</v>
+        <v>122234283</v>
       </c>
       <c r="B27" t="n">
-        <v>78639</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3394,37 +3364,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563095</v>
+        <v>563202</v>
       </c>
       <c r="R27" t="n">
-        <v>7040157</v>
+        <v>7040231</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3451,9 +3426,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,22 +3458,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233750</v>
+        <v>122233260</v>
       </c>
       <c r="B28" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563040</v>
+        <v>562896</v>
       </c>
       <c r="R28" t="n">
-        <v>7040180</v>
+        <v>7040281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3560,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3570,12 +3560,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3590,22 +3580,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122233933</v>
+        <v>122234125</v>
       </c>
       <c r="B29" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,7 +3628,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3647,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563089</v>
+        <v>563092</v>
       </c>
       <c r="R29" t="n">
-        <v>7040225</v>
+        <v>7040220</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,7 +3672,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3692,12 +3682,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233625</v>
+        <v>122233350</v>
       </c>
       <c r="B30" t="n">
-        <v>79720</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,37 +3730,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562978</v>
+        <v>562930</v>
       </c>
       <c r="R30" t="n">
-        <v>7040170</v>
+        <v>7040221</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3797,9 +3792,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,22 +3824,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234052</v>
+        <v>122234058</v>
       </c>
       <c r="B31" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3862,7 +3872,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3871,10 +3881,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563109</v>
+        <v>563095</v>
       </c>
       <c r="R31" t="n">
-        <v>7040194</v>
+        <v>7040206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3906,7 +3916,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3916,12 +3926,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234359</v>
+        <v>122233625</v>
       </c>
       <c r="B32" t="n">
-        <v>82426</v>
+        <v>79724</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3964,37 +3974,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563205</v>
+        <v>562978</v>
       </c>
       <c r="R32" t="n">
-        <v>7040240</v>
+        <v>7040170</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4021,19 +4031,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,22 +4048,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233647</v>
+        <v>122232949</v>
       </c>
       <c r="B33" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562988</v>
+        <v>562836</v>
       </c>
       <c r="R33" t="n">
-        <v>7040196</v>
+        <v>7040209</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4170,22 +4170,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233350</v>
+        <v>122234000</v>
       </c>
       <c r="B34" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4223,14 +4223,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562930</v>
+        <v>563097</v>
       </c>
       <c r="R34" t="n">
-        <v>7040221</v>
+        <v>7040210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,12 +4292,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
         <v>122233345</v>
       </c>
       <c r="B35" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122232469</v>
+        <v>122234038</v>
       </c>
       <c r="B36" t="n">
-        <v>90754</v>
+        <v>57372</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4442,37 +4442,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562748</v>
+        <v>563099</v>
       </c>
       <c r="R36" t="n">
-        <v>7040047</v>
+        <v>7040205</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4499,9 +4504,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4516,22 +4536,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234103</v>
+        <v>122234052</v>
       </c>
       <c r="B37" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4569,14 +4589,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563089</v>
+        <v>563109</v>
       </c>
       <c r="R37" t="n">
-        <v>7040216</v>
+        <v>7040194</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,7 +4628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4618,12 +4638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,22 +4658,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122234058</v>
+        <v>122233646</v>
       </c>
       <c r="B38" t="n">
-        <v>57369</v>
+        <v>79725</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4666,42 +4686,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563095</v>
+        <v>562989</v>
       </c>
       <c r="R38" t="n">
-        <v>7040206</v>
+        <v>7040172</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4728,24 +4743,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,22 +4760,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232270</v>
+        <v>122232285</v>
       </c>
       <c r="B39" t="n">
-        <v>79720</v>
+        <v>79724</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562828</v>
+        <v>562818</v>
       </c>
       <c r="R39" t="n">
-        <v>7040062</v>
+        <v>7040065</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122234038</v>
+        <v>122233750</v>
       </c>
       <c r="B40" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4915,14 +4915,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563099</v>
+        <v>563040</v>
       </c>
       <c r="R40" t="n">
-        <v>7040205</v>
+        <v>7040180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +4984,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234176</v>
+        <v>122233933</v>
       </c>
       <c r="B41" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5032,19 +5032,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563102</v>
+        <v>563089</v>
       </c>
       <c r="R41" t="n">
-        <v>7040234</v>
+        <v>7040225</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5121,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234359</v>
+        <v>122233260</v>
       </c>
       <c r="B11" t="n">
-        <v>82430</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563205</v>
+        <v>562896</v>
       </c>
       <c r="R11" t="n">
-        <v>7040240</v>
+        <v>7040281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,7 +1683,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233673</v>
+        <v>122234052</v>
       </c>
       <c r="B12" t="n">
-        <v>79760</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1727,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562986</v>
+        <v>563109</v>
       </c>
       <c r="R12" t="n">
-        <v>7040156</v>
+        <v>7040194</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,9 +1793,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1825,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233647</v>
+        <v>122233994</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,39 +1853,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562988</v>
+        <v>563088</v>
       </c>
       <c r="R13" t="n">
-        <v>7040196</v>
+        <v>7040175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,12 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122232469</v>
+        <v>122233345</v>
       </c>
       <c r="B14" t="n">
-        <v>90761</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,37 +1965,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562748</v>
+        <v>562904</v>
       </c>
       <c r="R14" t="n">
-        <v>7040047</v>
+        <v>7040280</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,9 +2027,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2059,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122232402</v>
+        <v>122234038</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,27 +2105,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562786</v>
+        <v>563099</v>
       </c>
       <c r="R15" t="n">
-        <v>7040064</v>
+        <v>7040205</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,14 +2149,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,22 +2181,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122234194</v>
+        <v>122233750</v>
       </c>
       <c r="B16" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,34 +2209,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563154</v>
+        <v>563040</v>
       </c>
       <c r="R16" t="n">
-        <v>7040221</v>
+        <v>7040180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2231,7 +2283,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122234176</v>
+        <v>122233127</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,39 +2331,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563102</v>
+        <v>562875</v>
       </c>
       <c r="R17" t="n">
-        <v>7040234</v>
+        <v>7040276</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,12 +2400,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122232932</v>
+        <v>122233673</v>
       </c>
       <c r="B18" t="n">
-        <v>82430</v>
+        <v>79762</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,25 +2439,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562795</v>
+        <v>562986</v>
       </c>
       <c r="R18" t="n">
-        <v>7040090</v>
+        <v>7040156</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2482,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233997</v>
+        <v>122233625</v>
       </c>
       <c r="B19" t="n">
-        <v>78643</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563095</v>
+        <v>562978</v>
       </c>
       <c r="R19" t="n">
-        <v>7040157</v>
+        <v>7040170</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2584,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122234103</v>
+        <v>122234359</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>82432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,39 +2647,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563089</v>
+        <v>563205</v>
       </c>
       <c r="R20" t="n">
-        <v>7040216</v>
+        <v>7040240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2706,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,12 +2716,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,22 +2731,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233994</v>
+        <v>122234103</v>
       </c>
       <c r="B21" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,34 +2759,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563088</v>
+        <v>563089</v>
       </c>
       <c r="R21" t="n">
-        <v>7040175</v>
+        <v>7040216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2791,7 +2833,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2806,22 +2853,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122233217</v>
+        <v>122234176</v>
       </c>
       <c r="B22" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,34 +2881,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562922</v>
+        <v>563102</v>
       </c>
       <c r="R22" t="n">
-        <v>7040240</v>
+        <v>7040234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2945,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2903,7 +2955,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2918,22 +2975,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233127</v>
+        <v>122232495</v>
       </c>
       <c r="B23" t="n">
-        <v>79724</v>
+        <v>79726</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,13 +3027,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562875</v>
+        <v>562748</v>
       </c>
       <c r="R23" t="n">
-        <v>7040276</v>
+        <v>7040046</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3003,19 +3060,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3030,22 +3077,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122232495</v>
+        <v>122233350</v>
       </c>
       <c r="B24" t="n">
-        <v>79724</v>
+        <v>57374</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,37 +3105,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562748</v>
+        <v>562930</v>
       </c>
       <c r="R24" t="n">
-        <v>7040046</v>
+        <v>7040221</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3115,9 +3167,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,22 +3199,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122232270</v>
+        <v>122233646</v>
       </c>
       <c r="B25" t="n">
-        <v>79724</v>
+        <v>79727</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3160,21 +3227,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3184,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562828</v>
+        <v>562989</v>
       </c>
       <c r="R25" t="n">
-        <v>7040062</v>
+        <v>7040172</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3246,10 +3313,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232184</v>
+        <v>122232469</v>
       </c>
       <c r="B26" t="n">
-        <v>78643</v>
+        <v>90763</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3262,21 +3329,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562833</v>
+        <v>562748</v>
       </c>
       <c r="R26" t="n">
-        <v>7040085</v>
+        <v>7040047</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3348,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122234283</v>
+        <v>122233217</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,39 +3431,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563202</v>
+        <v>562922</v>
       </c>
       <c r="R27" t="n">
-        <v>7040231</v>
+        <v>7040240</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3428,7 +3490,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3438,12 +3500,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,10 +3527,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233260</v>
+        <v>122234058</v>
       </c>
       <c r="B28" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,19 +3563,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562896</v>
+        <v>563095</v>
       </c>
       <c r="R28" t="n">
-        <v>7040281</v>
+        <v>7040206</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3560,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3592,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234125</v>
+        <v>122232402</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3626,24 +3683,27 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563092</v>
+        <v>562786</v>
       </c>
       <c r="R29" t="n">
-        <v>7040220</v>
+        <v>7040064</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3670,24 +3730,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3702,22 +3752,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233350</v>
+        <v>122233933</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3759,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562930</v>
+        <v>563089</v>
       </c>
       <c r="R30" t="n">
-        <v>7040221</v>
+        <v>7040225</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,7 +3844,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3804,12 +3854,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,22 +3874,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234058</v>
+        <v>122232932</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>82432</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3852,42 +3902,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563095</v>
+        <v>562795</v>
       </c>
       <c r="R31" t="n">
-        <v>7040206</v>
+        <v>7040090</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3914,24 +3959,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,22 +3976,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122233625</v>
+        <v>122234283</v>
       </c>
       <c r="B32" t="n">
-        <v>79724</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3974,37 +4004,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562978</v>
+        <v>563202</v>
       </c>
       <c r="R32" t="n">
-        <v>7040170</v>
+        <v>7040231</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4031,9 +4066,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,22 +4098,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122232949</v>
+        <v>122232184</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4076,42 +4126,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562836</v>
+        <v>562833</v>
       </c>
       <c r="R33" t="n">
-        <v>7040209</v>
+        <v>7040085</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,24 +4183,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4170,22 +4200,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122234000</v>
+        <v>122234125</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4218,19 +4248,19 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563097</v>
+        <v>563092</v>
       </c>
       <c r="R34" t="n">
-        <v>7040210</v>
+        <v>7040220</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,7 +4292,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4272,12 +4302,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,10 +4334,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233345</v>
+        <v>122233647</v>
       </c>
       <c r="B35" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4349,10 +4379,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562904</v>
+        <v>562988</v>
       </c>
       <c r="R35" t="n">
-        <v>7040280</v>
+        <v>7040196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4414,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,12 +4424,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4414,22 +4444,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234038</v>
+        <v>122232270</v>
       </c>
       <c r="B36" t="n">
-        <v>57372</v>
+        <v>79726</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4442,42 +4472,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563099</v>
+        <v>562828</v>
       </c>
       <c r="R36" t="n">
-        <v>7040205</v>
+        <v>7040062</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4504,24 +4529,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4536,22 +4546,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234052</v>
+        <v>122232949</v>
       </c>
       <c r="B37" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4589,14 +4599,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563109</v>
+        <v>562836</v>
       </c>
       <c r="R37" t="n">
-        <v>7040194</v>
+        <v>7040209</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4628,7 +4638,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4638,12 +4648,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,22 +4668,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233646</v>
+        <v>122233997</v>
       </c>
       <c r="B38" t="n">
-        <v>79725</v>
+        <v>78645</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4686,21 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4710,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562989</v>
+        <v>563095</v>
       </c>
       <c r="R38" t="n">
-        <v>7040172</v>
+        <v>7040157</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4772,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232285</v>
+        <v>122234194</v>
       </c>
       <c r="B39" t="n">
-        <v>79724</v>
+        <v>78645</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4788,37 +4798,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562818</v>
+        <v>563154</v>
       </c>
       <c r="R39" t="n">
-        <v>7040065</v>
+        <v>7040221</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4845,9 +4855,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,22 +4882,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233750</v>
+        <v>122232285</v>
       </c>
       <c r="B40" t="n">
-        <v>57372</v>
+        <v>79726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4890,42 +4910,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563040</v>
+        <v>562818</v>
       </c>
       <c r="R40" t="n">
-        <v>7040180</v>
+        <v>7040065</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4952,24 +4967,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +4984,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122233933</v>
+        <v>122234000</v>
       </c>
       <c r="B41" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5037,14 +5037,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563089</v>
+        <v>563097</v>
       </c>
       <c r="R41" t="n">
-        <v>7040225</v>
+        <v>7040210</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5121,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>79592</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233260</v>
+        <v>122233997</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562896</v>
+        <v>563095</v>
       </c>
       <c r="R11" t="n">
-        <v>7040281</v>
+        <v>7040157</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,24 +1666,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,19 +1683,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234052</v>
+        <v>122234000</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1760,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563109</v>
+        <v>563097</v>
       </c>
       <c r="R12" t="n">
-        <v>7040194</v>
+        <v>7040210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1775,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1805,12 +1785,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233994</v>
+        <v>122234103</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,34 +1833,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563088</v>
+        <v>563089</v>
       </c>
       <c r="R13" t="n">
-        <v>7040175</v>
+        <v>7040216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1897,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1907,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,22 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233345</v>
+        <v>122233217</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,39 +1955,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562904</v>
+        <v>562922</v>
       </c>
       <c r="R14" t="n">
-        <v>7040280</v>
+        <v>7040240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,12 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,19 +2039,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234038</v>
+        <v>122233345</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2112,14 +2092,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563099</v>
+        <v>562904</v>
       </c>
       <c r="R15" t="n">
-        <v>7040205</v>
+        <v>7040280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2193,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233750</v>
+        <v>122232270</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,42 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563040</v>
+        <v>562828</v>
       </c>
       <c r="R16" t="n">
-        <v>7040180</v>
+        <v>7040062</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2271,24 +2246,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,19 +2263,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233127</v>
+        <v>122233625</v>
       </c>
       <c r="B17" t="n">
         <v>79726</v>
@@ -2355,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562875</v>
+        <v>562978</v>
       </c>
       <c r="R17" t="n">
-        <v>7040276</v>
+        <v>7040170</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2388,19 +2348,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,22 +2365,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233673</v>
+        <v>122234283</v>
       </c>
       <c r="B18" t="n">
-        <v>79762</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,41 +2389,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562986</v>
+        <v>563202</v>
       </c>
       <c r="R18" t="n">
-        <v>7040156</v>
+        <v>7040231</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,9 +2455,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,22 +2487,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233625</v>
+        <v>122234359</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>82432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2545,37 +2515,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562978</v>
+        <v>563205</v>
       </c>
       <c r="R19" t="n">
-        <v>7040170</v>
+        <v>7040240</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,9 +2572,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,22 +2599,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122234359</v>
+        <v>122234125</v>
       </c>
       <c r="B20" t="n">
-        <v>82432</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,34 +2627,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563205</v>
+        <v>563092</v>
       </c>
       <c r="R20" t="n">
-        <v>7040240</v>
+        <v>7040220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2716,7 +2701,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,22 +2721,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122234103</v>
+        <v>122232469</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>90763</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,42 +2749,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563089</v>
+        <v>562748</v>
       </c>
       <c r="R21" t="n">
-        <v>7040216</v>
+        <v>7040047</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2821,24 +2806,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,19 +2823,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122234176</v>
+        <v>122232402</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2899,24 +2869,27 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563102</v>
+        <v>562786</v>
       </c>
       <c r="R22" t="n">
-        <v>7040234</v>
+        <v>7040064</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2943,24 +2916,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2938,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3089,7 +3052,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233350</v>
+        <v>122233260</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3134,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562930</v>
+        <v>562896</v>
       </c>
       <c r="R24" t="n">
-        <v>7040221</v>
+        <v>7040281</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3132,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,12 +3142,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3199,22 +3162,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233646</v>
+        <v>122234052</v>
       </c>
       <c r="B25" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3227,37 +3190,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562989</v>
+        <v>563109</v>
       </c>
       <c r="R25" t="n">
-        <v>7040172</v>
+        <v>7040194</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3284,9 +3252,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3301,22 +3284,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232469</v>
+        <v>122233994</v>
       </c>
       <c r="B26" t="n">
-        <v>90763</v>
+        <v>78645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3329,21 +3312,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3353,13 +3336,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562748</v>
+        <v>563088</v>
       </c>
       <c r="R26" t="n">
-        <v>7040047</v>
+        <v>7040175</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3386,9 +3369,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,22 +3396,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233217</v>
+        <v>122233750</v>
       </c>
       <c r="B27" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3431,34 +3424,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562922</v>
+        <v>563040</v>
       </c>
       <c r="R27" t="n">
-        <v>7040240</v>
+        <v>7040180</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,7 +3488,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3500,7 +3498,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3527,7 +3530,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122234058</v>
+        <v>122233647</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3563,19 +3566,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563095</v>
+        <v>562988</v>
       </c>
       <c r="R28" t="n">
-        <v>7040206</v>
+        <v>7040196</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,12 +3620,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,19 +3640,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232402</v>
+        <v>122233350</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3683,27 +3686,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562786</v>
+        <v>562930</v>
       </c>
       <c r="R29" t="n">
-        <v>7040064</v>
+        <v>7040221</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,14 +3730,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,19 +3762,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233933</v>
+        <v>122234058</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3800,19 +3810,19 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563089</v>
+        <v>563095</v>
       </c>
       <c r="R30" t="n">
-        <v>7040225</v>
+        <v>7040206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3844,7 +3854,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,12 +3864,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3886,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232932</v>
+        <v>122234038</v>
       </c>
       <c r="B31" t="n">
-        <v>82432</v>
+        <v>57374</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3902,37 +3912,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562795</v>
+        <v>563099</v>
       </c>
       <c r="R31" t="n">
-        <v>7040090</v>
+        <v>7040205</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3959,9 +3974,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,22 +4006,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234283</v>
+        <v>122232285</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,42 +4034,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563202</v>
+        <v>562818</v>
       </c>
       <c r="R32" t="n">
-        <v>7040231</v>
+        <v>7040065</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4066,24 +4091,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4098,22 +4108,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122232184</v>
+        <v>122233933</v>
       </c>
       <c r="B33" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4126,37 +4136,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562833</v>
+        <v>563089</v>
       </c>
       <c r="R33" t="n">
-        <v>7040085</v>
+        <v>7040225</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4183,9 +4198,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4200,22 +4230,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122234125</v>
+        <v>122233127</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4228,39 +4258,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563092</v>
+        <v>562875</v>
       </c>
       <c r="R34" t="n">
-        <v>7040220</v>
+        <v>7040276</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4292,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4302,12 +4327,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,10 +4354,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233647</v>
+        <v>122232932</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>82432</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4350,42 +4370,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562988</v>
+        <v>562795</v>
       </c>
       <c r="R35" t="n">
-        <v>7040196</v>
+        <v>7040090</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4412,24 +4427,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,22 +4444,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122232270</v>
+        <v>122232184</v>
       </c>
       <c r="B36" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562828</v>
+        <v>562833</v>
       </c>
       <c r="R36" t="n">
-        <v>7040062</v>
+        <v>7040085</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122232949</v>
+        <v>122233673</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>79762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,46 +4570,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562836</v>
+        <v>562986</v>
       </c>
       <c r="R37" t="n">
-        <v>7040209</v>
+        <v>7040156</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4636,24 +4631,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4668,22 +4648,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233997</v>
+        <v>122234176</v>
       </c>
       <c r="B38" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,37 +4676,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563095</v>
+        <v>563102</v>
       </c>
       <c r="R38" t="n">
-        <v>7040157</v>
+        <v>7040234</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,9 +4738,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,22 +4770,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122234194</v>
+        <v>122233646</v>
       </c>
       <c r="B39" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,37 +4798,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563154</v>
+        <v>562989</v>
       </c>
       <c r="R39" t="n">
-        <v>7040221</v>
+        <v>7040172</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4855,19 +4855,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,22 +4872,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122232285</v>
+        <v>122234194</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,37 +4900,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562818</v>
+        <v>563154</v>
       </c>
       <c r="R40" t="n">
-        <v>7040065</v>
+        <v>7040221</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,9 +4957,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,19 +4984,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234000</v>
+        <v>122232949</v>
       </c>
       <c r="B41" t="n">
         <v>57374</v>
@@ -5037,14 +5037,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563097</v>
+        <v>562836</v>
       </c>
       <c r="R41" t="n">
-        <v>7040210</v>
+        <v>7040209</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122232469</v>
+        <v>122234000</v>
       </c>
       <c r="B11" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1609,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562748</v>
+        <v>563097</v>
       </c>
       <c r="R11" t="n">
-        <v>7040047</v>
+        <v>7040210</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1671,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233994</v>
+        <v>122234058</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1731,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563088</v>
+        <v>563095</v>
       </c>
       <c r="R12" t="n">
-        <v>7040175</v>
+        <v>7040206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1780,7 +1805,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1825,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233750</v>
+        <v>122233997</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,42 +1853,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563040</v>
+        <v>563095</v>
       </c>
       <c r="R13" t="n">
-        <v>7040180</v>
+        <v>7040157</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,24 +1910,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,19 +1927,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122234103</v>
+        <v>122233345</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563089</v>
+        <v>562904</v>
       </c>
       <c r="R14" t="n">
-        <v>7040216</v>
+        <v>7040280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2019,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233625</v>
+        <v>122234052</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,37 +2077,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562978</v>
+        <v>563109</v>
       </c>
       <c r="R15" t="n">
-        <v>7040170</v>
+        <v>7040194</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,9 +2139,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,22 +2171,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122234194</v>
+        <v>122232469</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>90779</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,37 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563154</v>
+        <v>562748</v>
       </c>
       <c r="R16" t="n">
-        <v>7040221</v>
+        <v>7040047</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2226,19 +2256,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122232184</v>
+        <v>122233646</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562833</v>
+        <v>562989</v>
       </c>
       <c r="R17" t="n">
-        <v>7040085</v>
+        <v>7040172</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2367,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122232932</v>
+        <v>122234125</v>
       </c>
       <c r="B18" t="n">
-        <v>82432</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,37 +2403,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562795</v>
+        <v>563092</v>
       </c>
       <c r="R18" t="n">
-        <v>7040090</v>
+        <v>7040220</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,9 +2465,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,19 +2497,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233933</v>
+        <v>122234038</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2510,14 +2550,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563089</v>
+        <v>563099</v>
       </c>
       <c r="R19" t="n">
-        <v>7040225</v>
+        <v>7040205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2559,12 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122234125</v>
+        <v>122232184</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,42 +2769,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563092</v>
+        <v>562833</v>
       </c>
       <c r="R21" t="n">
-        <v>7040220</v>
+        <v>7040085</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2791,24 +2826,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,22 +2843,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232402</v>
+        <v>122232270</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,42 +2871,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562786</v>
+        <v>562828</v>
       </c>
       <c r="R22" t="n">
-        <v>7040064</v>
+        <v>7040062</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2919,11 +2931,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122232285</v>
+        <v>122233994</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,21 +2973,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2990,13 +2997,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562818</v>
+        <v>563088</v>
       </c>
       <c r="R23" t="n">
-        <v>7040065</v>
+        <v>7040175</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,9 +3030,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,22 +3057,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234359</v>
+        <v>122233673</v>
       </c>
       <c r="B24" t="n">
-        <v>82432</v>
+        <v>79762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,41 +3081,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563205</v>
+        <v>562986</v>
       </c>
       <c r="R24" t="n">
-        <v>7040240</v>
+        <v>7040156</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3125,19 +3142,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,19 +3159,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122234283</v>
+        <v>122232949</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3200,19 +3207,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563202</v>
+        <v>562836</v>
       </c>
       <c r="R25" t="n">
-        <v>7040231</v>
+        <v>7040209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3254,12 +3261,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,19 +3281,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122233127</v>
+        <v>122232285</v>
       </c>
       <c r="B26" t="n">
         <v>79726</v>
@@ -3326,13 +3333,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562875</v>
+        <v>562818</v>
       </c>
       <c r="R26" t="n">
-        <v>7040276</v>
+        <v>7040065</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3359,19 +3366,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,22 +3383,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122234000</v>
+        <v>122232495</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3414,42 +3411,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563097</v>
+        <v>562748</v>
       </c>
       <c r="R27" t="n">
-        <v>7040210</v>
+        <v>7040046</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3476,24 +3468,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,12 +3485,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3642,7 +3619,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122233345</v>
+        <v>122234283</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3678,19 +3655,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562904</v>
+        <v>563202</v>
       </c>
       <c r="R29" t="n">
-        <v>7040280</v>
+        <v>7040231</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3722,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3732,12 +3709,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,22 +3729,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233997</v>
+        <v>122234359</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>82432</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3780,37 +3757,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563095</v>
+        <v>563205</v>
       </c>
       <c r="R30" t="n">
-        <v>7040157</v>
+        <v>7040240</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,9 +3814,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,22 +3841,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122233673</v>
+        <v>122233750</v>
       </c>
       <c r="B31" t="n">
-        <v>79762</v>
+        <v>57374</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3878,41 +3865,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562986</v>
+        <v>563040</v>
       </c>
       <c r="R31" t="n">
-        <v>7040156</v>
+        <v>7040180</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,9 +3931,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,19 +3963,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234176</v>
+        <v>122234103</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -4004,19 +4011,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563102</v>
+        <v>563089</v>
       </c>
       <c r="R32" t="n">
-        <v>7040234</v>
+        <v>7040216</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,7 +4055,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4058,7 +4065,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4090,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122232495</v>
+        <v>122232402</v>
       </c>
       <c r="B33" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4106,34 +4113,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562748</v>
+        <v>562786</v>
       </c>
       <c r="R33" t="n">
-        <v>7040046</v>
+        <v>7040064</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4166,6 +4181,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4192,10 +4212,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233646</v>
+        <v>122233933</v>
       </c>
       <c r="B34" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,37 +4228,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562989</v>
+        <v>563089</v>
       </c>
       <c r="R34" t="n">
-        <v>7040172</v>
+        <v>7040225</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4265,9 +4290,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,22 +4322,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233647</v>
+        <v>122234194</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4310,39 +4350,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562988</v>
+        <v>563154</v>
       </c>
       <c r="R35" t="n">
-        <v>7040196</v>
+        <v>7040221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,7 +4409,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4384,12 +4419,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4416,10 +4446,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234038</v>
+        <v>122233217</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4432,39 +4462,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563099</v>
+        <v>562922</v>
       </c>
       <c r="R36" t="n">
-        <v>7040205</v>
+        <v>7040240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,7 +4521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4506,12 +4531,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,22 +4546,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234052</v>
+        <v>122233625</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4554,42 +4574,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563109</v>
+        <v>562978</v>
       </c>
       <c r="R37" t="n">
-        <v>7040194</v>
+        <v>7040170</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4616,24 +4631,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,22 +4648,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233217</v>
+        <v>122233127</v>
       </c>
       <c r="B38" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562922</v>
+        <v>562875</v>
       </c>
       <c r="R38" t="n">
-        <v>7040240</v>
+        <v>7040276</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,22 +4760,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232949</v>
+        <v>122232932</v>
       </c>
       <c r="B39" t="n">
-        <v>57374</v>
+        <v>82432</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4788,42 +4788,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562836</v>
+        <v>562795</v>
       </c>
       <c r="R39" t="n">
-        <v>7040209</v>
+        <v>7040090</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4850,24 +4845,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,22 +4862,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122232270</v>
+        <v>122233647</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,37 +4890,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562828</v>
+        <v>562988</v>
       </c>
       <c r="R40" t="n">
-        <v>7040062</v>
+        <v>7040196</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,9 +4952,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,19 +4984,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234058</v>
+        <v>122234176</v>
       </c>
       <c r="B41" t="n">
         <v>57374</v>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563095</v>
+        <v>563102</v>
       </c>
       <c r="R41" t="n">
-        <v>7040206</v>
+        <v>7040234</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234000</v>
+        <v>122233997</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563097</v>
+        <v>563095</v>
       </c>
       <c r="R11" t="n">
-        <v>7040210</v>
+        <v>7040157</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,24 +1666,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,19 +1683,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234058</v>
+        <v>122234000</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1751,7 +1731,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1760,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563095</v>
+        <v>563097</v>
       </c>
       <c r="R12" t="n">
-        <v>7040206</v>
+        <v>7040210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1775,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1805,12 +1785,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233997</v>
+        <v>122234058</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,37 +1833,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>563095</v>
       </c>
       <c r="R13" t="n">
-        <v>7040157</v>
+        <v>7040206</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,9 +1895,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233350</v>
+        <v>122232184</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,42 +2647,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562930</v>
+        <v>562833</v>
       </c>
       <c r="R20" t="n">
-        <v>7040221</v>
+        <v>7040085</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2709,24 +2704,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,22 +2721,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122232184</v>
+        <v>122232270</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2793,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562833</v>
+        <v>562828</v>
       </c>
       <c r="R21" t="n">
-        <v>7040085</v>
+        <v>7040062</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2855,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232270</v>
+        <v>122233350</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,37 +2851,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562828</v>
+        <v>562930</v>
       </c>
       <c r="R22" t="n">
-        <v>7040062</v>
+        <v>7040221</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,9 +2913,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,12 +2945,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233997</v>
+        <v>122233933</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1609,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563095</v>
+        <v>563089</v>
       </c>
       <c r="R11" t="n">
-        <v>7040157</v>
+        <v>7040225</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1671,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234000</v>
+        <v>122234359</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>82433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563097</v>
+        <v>563205</v>
       </c>
       <c r="R12" t="n">
-        <v>7040210</v>
+        <v>7040240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,7 +1790,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1785,12 +1800,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1815,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234058</v>
+        <v>122232932</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>82433</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,42 +1843,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563095</v>
+        <v>562795</v>
       </c>
       <c r="R13" t="n">
-        <v>7040206</v>
+        <v>7040090</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1895,24 +1900,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233345</v>
+        <v>122233997</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,42 +1945,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562904</v>
+        <v>563095</v>
       </c>
       <c r="R14" t="n">
-        <v>7040280</v>
+        <v>7040157</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,24 +2002,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,19 +2019,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234052</v>
+        <v>122234125</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2097,19 +2067,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563109</v>
+        <v>563092</v>
       </c>
       <c r="R15" t="n">
-        <v>7040194</v>
+        <v>7040220</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2111,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,12 +2121,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,22 +2141,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122232469</v>
+        <v>122233127</v>
       </c>
       <c r="B16" t="n">
-        <v>90779</v>
+        <v>79727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,13 +2193,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562748</v>
+        <v>562875</v>
       </c>
       <c r="R16" t="n">
-        <v>7040047</v>
+        <v>7040276</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2256,9 +2226,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,12 +2253,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2288,7 +2268,7 @@
         <v>122233646</v>
       </c>
       <c r="B17" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122234125</v>
+        <v>122233345</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2423,7 +2403,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2432,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563092</v>
+        <v>562904</v>
       </c>
       <c r="R18" t="n">
-        <v>7040220</v>
+        <v>7040280</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,12 +2457,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122234038</v>
+        <v>122234176</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2545,7 +2525,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2554,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563099</v>
+        <v>563102</v>
       </c>
       <c r="R19" t="n">
-        <v>7040205</v>
+        <v>7040234</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2599,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2631,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232184</v>
+        <v>122233750</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,37 +2627,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562833</v>
+        <v>563040</v>
       </c>
       <c r="R20" t="n">
-        <v>7040085</v>
+        <v>7040180</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,9 +2689,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,22 +2721,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122232270</v>
+        <v>122232184</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562828</v>
+        <v>562833</v>
       </c>
       <c r="R21" t="n">
-        <v>7040062</v>
+        <v>7040085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122233350</v>
+        <v>122232285</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,42 +2851,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562930</v>
+        <v>562818</v>
       </c>
       <c r="R22" t="n">
-        <v>7040221</v>
+        <v>7040065</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,24 +2908,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2925,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233994</v>
+        <v>122232949</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,34 +2953,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563088</v>
+        <v>562836</v>
       </c>
       <c r="R23" t="n">
-        <v>7040175</v>
+        <v>7040209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3027,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,22 +3047,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233673</v>
+        <v>122233350</v>
       </c>
       <c r="B24" t="n">
-        <v>79762</v>
+        <v>57374</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,41 +3071,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562986</v>
+        <v>562930</v>
       </c>
       <c r="R24" t="n">
-        <v>7040156</v>
+        <v>7040221</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3142,9 +3137,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,22 +3169,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122232949</v>
+        <v>122234194</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,39 +3197,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562836</v>
+        <v>563154</v>
       </c>
       <c r="R25" t="n">
-        <v>7040209</v>
+        <v>7040221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,12 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,22 +3281,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232285</v>
+        <v>122232495</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562818</v>
+        <v>562748</v>
       </c>
       <c r="R26" t="n">
-        <v>7040065</v>
+        <v>7040046</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122232495</v>
+        <v>122233994</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562748</v>
+        <v>563088</v>
       </c>
       <c r="R27" t="n">
-        <v>7040046</v>
+        <v>7040175</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,9 +3468,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,22 +3495,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233260</v>
+        <v>122232270</v>
       </c>
       <c r="B28" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,42 +3523,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562896</v>
+        <v>562828</v>
       </c>
       <c r="R28" t="n">
-        <v>7040281</v>
+        <v>7040062</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3575,24 +3580,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,19 +3597,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234283</v>
+        <v>122234052</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3655,7 +3645,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3664,10 +3654,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563202</v>
+        <v>563109</v>
       </c>
       <c r="R29" t="n">
-        <v>7040231</v>
+        <v>7040194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,7 +3689,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,12 +3699,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,10 +3731,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122234359</v>
+        <v>122232402</v>
       </c>
       <c r="B30" t="n">
-        <v>82432</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,37 +3747,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563205</v>
+        <v>562786</v>
       </c>
       <c r="R30" t="n">
-        <v>7040240</v>
+        <v>7040064</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3814,19 +3812,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3841,19 +3834,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122233750</v>
+        <v>122234058</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3889,19 +3882,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563040</v>
+        <v>563095</v>
       </c>
       <c r="R31" t="n">
-        <v>7040180</v>
+        <v>7040206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,7 +3926,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3943,12 +3936,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,22 +3956,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234103</v>
+        <v>122233625</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,42 +3984,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563089</v>
+        <v>562978</v>
       </c>
       <c r="R32" t="n">
-        <v>7040216</v>
+        <v>7040170</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,24 +4041,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,19 +4058,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122232402</v>
+        <v>122234103</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4131,27 +4104,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562786</v>
+        <v>563089</v>
       </c>
       <c r="R33" t="n">
-        <v>7040064</v>
+        <v>7040216</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4178,14 +4148,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4200,22 +4180,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233933</v>
+        <v>122233217</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4228,39 +4208,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563089</v>
+        <v>562922</v>
       </c>
       <c r="R34" t="n">
-        <v>7040225</v>
+        <v>7040240</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4292,7 +4267,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4302,12 +4277,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,22 +4292,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234194</v>
+        <v>122234000</v>
       </c>
       <c r="B35" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4350,34 +4320,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563154</v>
+        <v>563097</v>
       </c>
       <c r="R35" t="n">
-        <v>7040221</v>
+        <v>7040210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4409,7 +4384,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4419,7 +4394,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4434,22 +4414,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122233217</v>
+        <v>122232469</v>
       </c>
       <c r="B36" t="n">
-        <v>78645</v>
+        <v>90789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4462,21 +4442,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4486,13 +4466,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562922</v>
+        <v>562748</v>
       </c>
       <c r="R36" t="n">
-        <v>7040240</v>
+        <v>7040047</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4519,19 +4499,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,22 +4516,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122233625</v>
+        <v>122234038</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4574,37 +4544,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562978</v>
+        <v>563099</v>
       </c>
       <c r="R37" t="n">
-        <v>7040170</v>
+        <v>7040205</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4631,9 +4606,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,22 +4638,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233127</v>
+        <v>122234283</v>
       </c>
       <c r="B38" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4676,34 +4666,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562875</v>
+        <v>563202</v>
       </c>
       <c r="R38" t="n">
-        <v>7040276</v>
+        <v>7040231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4735,7 +4730,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4740,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,22 +4760,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232932</v>
+        <v>122233647</v>
       </c>
       <c r="B39" t="n">
-        <v>82432</v>
+        <v>57374</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4788,37 +4788,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562795</v>
+        <v>562988</v>
       </c>
       <c r="R39" t="n">
-        <v>7040090</v>
+        <v>7040196</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4845,9 +4850,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,22 +4882,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233647</v>
+        <v>122233673</v>
       </c>
       <c r="B40" t="n">
-        <v>57374</v>
+        <v>79763</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4886,46 +4906,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562988</v>
+        <v>562986</v>
       </c>
       <c r="R40" t="n">
-        <v>7040196</v>
+        <v>7040156</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4952,24 +4967,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,19 +4984,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234176</v>
+        <v>122233260</v>
       </c>
       <c r="B41" t="n">
         <v>57374</v>
@@ -5032,19 +5032,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563102</v>
+        <v>562896</v>
       </c>
       <c r="R41" t="n">
-        <v>7040234</v>
+        <v>7040281</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5121,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79592</v>
+        <v>79593</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5338,6 +5338,638 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122431200</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90807</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>563033</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7040085</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122431459</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>563214</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7040130</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122431113</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>562981</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7040158</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122431003</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>562919</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7040173</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122431528</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>563173</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7040184</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122431232</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>563034</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7040085</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233933</v>
+        <v>122233994</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,39 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563089</v>
+        <v>563088</v>
       </c>
       <c r="R11" t="n">
-        <v>7040225</v>
+        <v>7040175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1683,12 +1678,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234359</v>
+        <v>122232184</v>
       </c>
       <c r="B12" t="n">
-        <v>82433</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,37 +1721,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563205</v>
+        <v>562833</v>
       </c>
       <c r="R12" t="n">
-        <v>7040240</v>
+        <v>7040085</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,19 +1778,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122232932</v>
+        <v>122234000</v>
       </c>
       <c r="B13" t="n">
-        <v>82433</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,37 +1823,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562795</v>
+        <v>563097</v>
       </c>
       <c r="R13" t="n">
-        <v>7040090</v>
+        <v>7040210</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1900,9 +1885,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233997</v>
+        <v>122234058</v>
       </c>
       <c r="B14" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,37 +1945,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>563095</v>
       </c>
       <c r="R14" t="n">
-        <v>7040157</v>
+        <v>7040206</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,9 +2007,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,12 +2039,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2153,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233127</v>
+        <v>122232402</v>
       </c>
       <c r="B16" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,37 +2189,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562875</v>
+        <v>562786</v>
       </c>
       <c r="R16" t="n">
-        <v>7040276</v>
+        <v>7040064</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2226,19 +2254,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:41</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,22 +2276,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233646</v>
+        <v>122233933</v>
       </c>
       <c r="B17" t="n">
-        <v>79728</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,37 +2304,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562989</v>
+        <v>563089</v>
       </c>
       <c r="R17" t="n">
-        <v>7040172</v>
+        <v>7040225</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2366,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,19 +2398,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233345</v>
+        <v>122232949</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2412,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562904</v>
+        <v>562836</v>
       </c>
       <c r="R18" t="n">
-        <v>7040280</v>
+        <v>7040209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2490,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,12 +2500,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122234176</v>
+        <v>122232495</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,42 +2548,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>562748</v>
       </c>
       <c r="R19" t="n">
-        <v>7040234</v>
+        <v>7040046</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2567,24 +2605,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,19 +2622,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233750</v>
+        <v>122234176</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2647,19 +2670,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563040</v>
+        <v>563102</v>
       </c>
       <c r="R20" t="n">
-        <v>7040180</v>
+        <v>7040234</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,12 +2724,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,22 +2744,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122232184</v>
+        <v>122233345</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,37 +2772,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562833</v>
+        <v>562904</v>
       </c>
       <c r="R21" t="n">
-        <v>7040085</v>
+        <v>7040280</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,9 +2834,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,22 +2866,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232285</v>
+        <v>122234038</v>
       </c>
       <c r="B22" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,37 +2894,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562818</v>
+        <v>563099</v>
       </c>
       <c r="R22" t="n">
-        <v>7040065</v>
+        <v>7040205</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2908,9 +2956,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,22 +2988,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122232949</v>
+        <v>122232285</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,42 +3016,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562836</v>
+        <v>562818</v>
       </c>
       <c r="R23" t="n">
-        <v>7040209</v>
+        <v>7040065</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3015,24 +3073,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233350</v>
+        <v>122233997</v>
       </c>
       <c r="B24" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3075,42 +3118,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562930</v>
+        <v>563095</v>
       </c>
       <c r="R24" t="n">
-        <v>7040221</v>
+        <v>7040157</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3137,24 +3175,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,12 +3192,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3293,10 +3316,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232495</v>
+        <v>122234283</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3309,37 +3332,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562748</v>
+        <v>563202</v>
       </c>
       <c r="R26" t="n">
-        <v>7040046</v>
+        <v>7040231</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3366,9 +3394,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,22 +3426,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233994</v>
+        <v>122233646</v>
       </c>
       <c r="B27" t="n">
-        <v>78646</v>
+        <v>79728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,21 +3454,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3435,13 +3478,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563088</v>
+        <v>562989</v>
       </c>
       <c r="R27" t="n">
-        <v>7040175</v>
+        <v>7040172</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,19 +3511,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,22 +3528,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122232270</v>
+        <v>122233750</v>
       </c>
       <c r="B28" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3523,37 +3556,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562828</v>
+        <v>563040</v>
       </c>
       <c r="R28" t="n">
-        <v>7040062</v>
+        <v>7040180</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3580,9 +3618,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,19 +3650,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234052</v>
+        <v>122234103</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3650,14 +3703,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563109</v>
+        <v>563089</v>
       </c>
       <c r="R29" t="n">
-        <v>7040194</v>
+        <v>7040216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3689,7 +3742,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3699,12 +3752,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3719,22 +3772,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232402</v>
+        <v>122232270</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3747,42 +3800,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562786</v>
+        <v>562828</v>
       </c>
       <c r="R30" t="n">
-        <v>7040064</v>
+        <v>7040062</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3815,11 +3860,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3846,10 +3886,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234058</v>
+        <v>122232932</v>
       </c>
       <c r="B31" t="n">
-        <v>57374</v>
+        <v>82433</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3862,42 +3902,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563095</v>
+        <v>562795</v>
       </c>
       <c r="R31" t="n">
-        <v>7040206</v>
+        <v>7040090</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3924,24 +3959,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,22 +3976,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122233625</v>
+        <v>122233350</v>
       </c>
       <c r="B32" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3984,37 +4004,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562978</v>
+        <v>562930</v>
       </c>
       <c r="R32" t="n">
-        <v>7040170</v>
+        <v>7040221</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4041,9 +4066,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,19 +4098,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122234103</v>
+        <v>122233647</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4115,10 +4155,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563089</v>
+        <v>562988</v>
       </c>
       <c r="R33" t="n">
-        <v>7040216</v>
+        <v>7040196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,7 +4190,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4160,12 +4200,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4180,12 +4220,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4304,10 +4344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234000</v>
+        <v>122233127</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4320,39 +4360,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563097</v>
+        <v>562875</v>
       </c>
       <c r="R35" t="n">
-        <v>7040210</v>
+        <v>7040276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4419,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,12 +4429,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4426,10 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122232469</v>
+        <v>122234052</v>
       </c>
       <c r="B36" t="n">
-        <v>90789</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4442,37 +4472,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562748</v>
+        <v>563109</v>
       </c>
       <c r="R36" t="n">
-        <v>7040047</v>
+        <v>7040194</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4499,9 +4534,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4516,22 +4566,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234038</v>
+        <v>122232469</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>90789</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4544,42 +4594,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563099</v>
+        <v>562748</v>
       </c>
       <c r="R37" t="n">
-        <v>7040205</v>
+        <v>7040047</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4606,24 +4651,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,22 +4668,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122234283</v>
+        <v>122233673</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>79763</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4662,46 +4692,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563202</v>
+        <v>562986</v>
       </c>
       <c r="R38" t="n">
-        <v>7040231</v>
+        <v>7040156</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4728,24 +4753,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,19 +4770,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233647</v>
+        <v>122233260</v>
       </c>
       <c r="B39" t="n">
         <v>57374</v>
@@ -4817,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562988</v>
+        <v>562896</v>
       </c>
       <c r="R39" t="n">
-        <v>7040196</v>
+        <v>7040281</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4852,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4862,12 +4872,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,22 +4892,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233673</v>
+        <v>122234359</v>
       </c>
       <c r="B40" t="n">
-        <v>79763</v>
+        <v>82433</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4906,41 +4916,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562986</v>
+        <v>563205</v>
       </c>
       <c r="R40" t="n">
-        <v>7040156</v>
+        <v>7040240</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,9 +4977,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +5004,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122233260</v>
+        <v>122233625</v>
       </c>
       <c r="B41" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5012,42 +5032,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562896</v>
+        <v>562978</v>
       </c>
       <c r="R41" t="n">
-        <v>7040281</v>
+        <v>7040170</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5074,24 +5089,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431200</v>
+        <v>122431232</v>
       </c>
       <c r="B44" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563033</v>
+        <v>563034</v>
       </c>
       <c r="R44" t="n">
         <v>7040085</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431459</v>
+        <v>122431003</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,39 +5459,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563214</v>
+        <v>562919</v>
       </c>
       <c r="R45" t="n">
-        <v>7040130</v>
+        <v>7040173</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5524,11 +5519,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5667,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431003</v>
+        <v>122431528</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5683,34 +5673,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562919</v>
+        <v>563173</v>
       </c>
       <c r="R47" t="n">
-        <v>7040173</v>
+        <v>7040184</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5769,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431528</v>
+        <v>122431459</v>
       </c>
       <c r="B48" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5785,34 +5775,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563173</v>
+        <v>563214</v>
       </c>
       <c r="R48" t="n">
-        <v>7040184</v>
+        <v>7040130</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5845,6 +5840,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,10 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431232</v>
+        <v>122431200</v>
       </c>
       <c r="B49" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5887,21 +5887,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563034</v>
+        <v>563033</v>
       </c>
       <c r="R49" t="n">
         <v>7040085</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233994</v>
+        <v>122233127</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563088</v>
+        <v>562875</v>
       </c>
       <c r="R11" t="n">
-        <v>7040175</v>
+        <v>7040276</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122232184</v>
+        <v>122233997</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562833</v>
+        <v>563095</v>
       </c>
       <c r="R12" t="n">
-        <v>7040085</v>
+        <v>7040157</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234000</v>
+        <v>122233673</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>79768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,46 +1819,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563097</v>
+        <v>562986</v>
       </c>
       <c r="R13" t="n">
-        <v>7040210</v>
+        <v>7040156</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,24 +1880,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,12 +1897,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1932,7 +1912,7 @@
         <v>122234058</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234125</v>
+        <v>122234359</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>82438</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563092</v>
+        <v>563205</v>
       </c>
       <c r="R15" t="n">
-        <v>7040220</v>
+        <v>7040240</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2106,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,12 +2116,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,22 +2131,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122232402</v>
+        <v>122234194</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,45 +2159,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562786</v>
+        <v>563154</v>
       </c>
       <c r="R16" t="n">
-        <v>7040064</v>
+        <v>7040221</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,14 +2216,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,22 +2243,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233933</v>
+        <v>122233345</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563089</v>
+        <v>562904</v>
       </c>
       <c r="R17" t="n">
-        <v>7040225</v>
+        <v>7040280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,7 +2335,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2378,12 +2345,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,7 +2380,7 @@
         <v>122232949</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122232495</v>
+        <v>122233647</v>
       </c>
       <c r="B19" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,37 +2515,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562748</v>
+        <v>562988</v>
       </c>
       <c r="R19" t="n">
-        <v>7040046</v>
+        <v>7040196</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2605,9 +2577,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2622,22 +2609,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122234176</v>
+        <v>122233260</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2670,19 +2657,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563102</v>
+        <v>562896</v>
       </c>
       <c r="R20" t="n">
-        <v>7040234</v>
+        <v>7040281</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2756,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233345</v>
+        <v>122234052</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,14 +2784,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562904</v>
+        <v>563109</v>
       </c>
       <c r="R21" t="n">
-        <v>7040280</v>
+        <v>7040194</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,12 +2833,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,22 +2853,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122234038</v>
+        <v>122233217</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,39 +2881,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563099</v>
+        <v>562922</v>
       </c>
       <c r="R22" t="n">
-        <v>7040205</v>
+        <v>7040240</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,12 +2950,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,12 +2965,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3003,7 +2980,7 @@
         <v>122232285</v>
       </c>
       <c r="B23" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233997</v>
+        <v>122232184</v>
       </c>
       <c r="B24" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3142,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563095</v>
+        <v>562833</v>
       </c>
       <c r="R24" t="n">
-        <v>7040157</v>
+        <v>7040085</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3204,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122234194</v>
+        <v>122233750</v>
       </c>
       <c r="B25" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,34 +3197,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563154</v>
+        <v>563040</v>
       </c>
       <c r="R25" t="n">
-        <v>7040221</v>
+        <v>7040180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3289,7 +3271,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,10 +3303,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234283</v>
+        <v>122232932</v>
       </c>
       <c r="B26" t="n">
-        <v>57374</v>
+        <v>82438</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3332,42 +3319,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563202</v>
+        <v>562795</v>
       </c>
       <c r="R26" t="n">
-        <v>7040231</v>
+        <v>7040090</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3394,24 +3376,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,22 +3393,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233646</v>
+        <v>122233994</v>
       </c>
       <c r="B27" t="n">
-        <v>79728</v>
+        <v>78651</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3454,21 +3421,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3478,13 +3445,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562989</v>
+        <v>563088</v>
       </c>
       <c r="R27" t="n">
-        <v>7040172</v>
+        <v>7040175</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3511,9 +3478,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,22 +3505,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233750</v>
+        <v>122232495</v>
       </c>
       <c r="B28" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3556,42 +3533,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563040</v>
+        <v>562748</v>
       </c>
       <c r="R28" t="n">
-        <v>7040180</v>
+        <v>7040046</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3618,24 +3590,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,22 +3607,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234103</v>
+        <v>122234038</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3703,14 +3660,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563089</v>
+        <v>563099</v>
       </c>
       <c r="R29" t="n">
-        <v>7040216</v>
+        <v>7040205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3742,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3752,7 +3709,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3784,10 +3741,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232270</v>
+        <v>122234125</v>
       </c>
       <c r="B30" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,37 +3757,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562828</v>
+        <v>563092</v>
       </c>
       <c r="R30" t="n">
-        <v>7040062</v>
+        <v>7040220</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3857,9 +3819,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,22 +3851,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232932</v>
+        <v>122232469</v>
       </c>
       <c r="B31" t="n">
-        <v>82433</v>
+        <v>90801</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3902,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3926,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562795</v>
+        <v>562748</v>
       </c>
       <c r="R31" t="n">
-        <v>7040090</v>
+        <v>7040047</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3988,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122233350</v>
+        <v>122234176</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4024,19 +4001,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562930</v>
+        <v>563102</v>
       </c>
       <c r="R32" t="n">
-        <v>7040221</v>
+        <v>7040234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,7 +4045,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4078,12 +4055,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4098,22 +4075,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233647</v>
+        <v>122234103</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4155,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562988</v>
+        <v>563089</v>
       </c>
       <c r="R33" t="n">
-        <v>7040196</v>
+        <v>7040216</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4200,12 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4220,22 +4197,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233217</v>
+        <v>122233625</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4248,21 +4225,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4272,13 +4249,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562922</v>
+        <v>562978</v>
       </c>
       <c r="R34" t="n">
-        <v>7040240</v>
+        <v>7040170</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,19 +4282,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,22 +4299,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233127</v>
+        <v>122233646</v>
       </c>
       <c r="B35" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,21 +4327,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4384,13 +4351,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562875</v>
+        <v>562989</v>
       </c>
       <c r="R35" t="n">
-        <v>7040276</v>
+        <v>7040172</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4417,19 +4384,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,22 +4401,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234052</v>
+        <v>122234000</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4501,10 +4458,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563109</v>
+        <v>563097</v>
       </c>
       <c r="R36" t="n">
-        <v>7040194</v>
+        <v>7040210</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4536,7 +4493,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4546,12 +4503,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4566,22 +4523,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122232469</v>
+        <v>122234283</v>
       </c>
       <c r="B37" t="n">
-        <v>90789</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,37 +4551,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562748</v>
+        <v>563202</v>
       </c>
       <c r="R37" t="n">
-        <v>7040047</v>
+        <v>7040231</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4651,9 +4613,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4668,22 +4645,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233673</v>
+        <v>122233933</v>
       </c>
       <c r="B38" t="n">
-        <v>79763</v>
+        <v>57379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4692,41 +4669,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562986</v>
+        <v>563089</v>
       </c>
       <c r="R38" t="n">
-        <v>7040156</v>
+        <v>7040225</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,9 +4735,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,22 +4767,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233260</v>
+        <v>122232402</v>
       </c>
       <c r="B39" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4816,24 +4813,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562896</v>
+        <v>562786</v>
       </c>
       <c r="R39" t="n">
-        <v>7040281</v>
+        <v>7040064</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4860,24 +4860,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4892,22 +4882,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122234359</v>
+        <v>122233350</v>
       </c>
       <c r="B40" t="n">
-        <v>82433</v>
+        <v>57379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4920,34 +4910,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563205</v>
+        <v>562930</v>
       </c>
       <c r="R40" t="n">
-        <v>7040240</v>
+        <v>7040221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4979,7 +4974,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4989,7 +4984,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122233625</v>
+        <v>122232270</v>
       </c>
       <c r="B41" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562978</v>
+        <v>562828</v>
       </c>
       <c r="R41" t="n">
-        <v>7040170</v>
+        <v>7040062</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5121,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79593</v>
+        <v>79598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431232</v>
+        <v>122431003</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563034</v>
+        <v>562919</v>
       </c>
       <c r="R44" t="n">
-        <v>7040085</v>
+        <v>7040173</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431003</v>
+        <v>122431113</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,34 +5459,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562919</v>
+        <v>562981</v>
       </c>
       <c r="R45" t="n">
-        <v>7040173</v>
+        <v>7040158</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5519,6 +5524,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431113</v>
+        <v>122431528</v>
       </c>
       <c r="B46" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5561,39 +5571,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562981</v>
+        <v>563173</v>
       </c>
       <c r="R46" t="n">
-        <v>7040158</v>
+        <v>7040184</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5626,11 +5631,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431528</v>
+        <v>122431200</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>90819</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5673,34 +5673,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563173</v>
+        <v>563033</v>
       </c>
       <c r="R47" t="n">
-        <v>7040184</v>
+        <v>7040085</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431459</v>
+        <v>122431232</v>
       </c>
       <c r="B48" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,39 +5775,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563214</v>
+        <v>563034</v>
       </c>
       <c r="R48" t="n">
-        <v>7040130</v>
+        <v>7040085</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5840,11 +5835,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,10 +5861,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431200</v>
+        <v>122431459</v>
       </c>
       <c r="B49" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5887,34 +5877,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563033</v>
+        <v>563214</v>
       </c>
       <c r="R49" t="n">
-        <v>7040085</v>
+        <v>7040130</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5947,6 +5942,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233997</v>
+        <v>122234125</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,37 +1721,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563095</v>
+        <v>563092</v>
       </c>
       <c r="R12" t="n">
-        <v>7040157</v>
+        <v>7040220</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,9 +1783,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1815,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233673</v>
+        <v>122233997</v>
       </c>
       <c r="B13" t="n">
-        <v>79768</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562986</v>
+        <v>563095</v>
       </c>
       <c r="R13" t="n">
-        <v>7040156</v>
+        <v>7040157</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122234058</v>
+        <v>122233647</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1945,19 +1965,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563095</v>
+        <v>562988</v>
       </c>
       <c r="R14" t="n">
-        <v>7040206</v>
+        <v>7040196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1999,12 +2019,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2039,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234359</v>
+        <v>122232285</v>
       </c>
       <c r="B15" t="n">
-        <v>82438</v>
+        <v>79732</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,37 +2067,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563205</v>
+        <v>562818</v>
       </c>
       <c r="R15" t="n">
-        <v>7040240</v>
+        <v>7040065</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2104,19 +2124,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,19 +2141,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122234194</v>
+        <v>122233217</v>
       </c>
       <c r="B16" t="n">
         <v>78651</v>
@@ -2179,14 +2189,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563154</v>
+        <v>562922</v>
       </c>
       <c r="R16" t="n">
-        <v>7040221</v>
+        <v>7040240</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,7 +2228,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2228,7 +2238,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233345</v>
+        <v>122232184</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,42 +2281,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562904</v>
+        <v>562833</v>
       </c>
       <c r="R17" t="n">
-        <v>7040280</v>
+        <v>7040085</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2333,24 +2338,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,19 +2355,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122232949</v>
+        <v>122233350</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2422,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562836</v>
+        <v>562930</v>
       </c>
       <c r="R18" t="n">
-        <v>7040209</v>
+        <v>7040221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,12 +2457,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,19 +2477,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233647</v>
+        <v>122234176</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2535,19 +2525,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562988</v>
+        <v>563102</v>
       </c>
       <c r="R19" t="n">
-        <v>7040196</v>
+        <v>7040234</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,12 +2579,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,19 +2599,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233260</v>
+        <v>122233750</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2666,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562896</v>
+        <v>563040</v>
       </c>
       <c r="R20" t="n">
-        <v>7040281</v>
+        <v>7040180</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,12 +2701,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,19 +2721,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122234052</v>
+        <v>122233260</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2784,14 +2774,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563109</v>
+        <v>562896</v>
       </c>
       <c r="R21" t="n">
-        <v>7040194</v>
+        <v>7040281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2813,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,12 +2823,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,19 +2843,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122233217</v>
+        <v>122233994</v>
       </c>
       <c r="B22" t="n">
         <v>78651</v>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562922</v>
+        <v>563088</v>
       </c>
       <c r="R22" t="n">
-        <v>7040240</v>
+        <v>7040175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122232285</v>
+        <v>122232402</v>
       </c>
       <c r="B23" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2993,34 +2983,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562818</v>
+        <v>562786</v>
       </c>
       <c r="R23" t="n">
-        <v>7040065</v>
+        <v>7040064</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3053,6 +3051,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122232184</v>
+        <v>122232469</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>90808</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,21 +3098,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3122,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562833</v>
+        <v>562748</v>
       </c>
       <c r="R24" t="n">
-        <v>7040085</v>
+        <v>7040047</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3181,10 +3184,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233750</v>
+        <v>122232495</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,42 +3200,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563040</v>
+        <v>562748</v>
       </c>
       <c r="R25" t="n">
-        <v>7040180</v>
+        <v>7040046</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3259,24 +3257,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,22 +3274,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232932</v>
+        <v>122233345</v>
       </c>
       <c r="B26" t="n">
-        <v>82438</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3319,37 +3302,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562795</v>
+        <v>562904</v>
       </c>
       <c r="R26" t="n">
-        <v>7040090</v>
+        <v>7040280</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3376,9 +3364,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,22 +3396,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233994</v>
+        <v>122233673</v>
       </c>
       <c r="B27" t="n">
-        <v>78651</v>
+        <v>79768</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3417,25 +3420,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3445,13 +3448,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563088</v>
+        <v>562986</v>
       </c>
       <c r="R27" t="n">
-        <v>7040175</v>
+        <v>7040156</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3478,19 +3481,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,22 +3498,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122232495</v>
+        <v>122234359</v>
       </c>
       <c r="B28" t="n">
-        <v>79732</v>
+        <v>82438</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,37 +3526,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562748</v>
+        <v>563205</v>
       </c>
       <c r="R28" t="n">
-        <v>7040046</v>
+        <v>7040240</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,9 +3583,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,22 +3610,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234038</v>
+        <v>122232932</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>82438</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,42 +3638,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563099</v>
+        <v>562795</v>
       </c>
       <c r="R29" t="n">
-        <v>7040205</v>
+        <v>7040090</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3697,24 +3695,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,19 +3712,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122234125</v>
+        <v>122232949</v>
       </c>
       <c r="B30" t="n">
         <v>57379</v>
@@ -3777,7 +3760,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3786,10 +3769,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563092</v>
+        <v>562836</v>
       </c>
       <c r="R30" t="n">
-        <v>7040220</v>
+        <v>7040209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3821,7 +3804,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3831,12 +3814,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,10 +3846,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232469</v>
+        <v>122234283</v>
       </c>
       <c r="B31" t="n">
-        <v>90801</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3879,37 +3862,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562748</v>
+        <v>563202</v>
       </c>
       <c r="R31" t="n">
-        <v>7040047</v>
+        <v>7040231</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3924,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,22 +3956,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234176</v>
+        <v>122232270</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3981,42 +3984,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563102</v>
+        <v>562828</v>
       </c>
       <c r="R32" t="n">
-        <v>7040234</v>
+        <v>7040062</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4043,24 +4041,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,22 +4058,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122234103</v>
+        <v>122234194</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4103,39 +4086,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563089</v>
+        <v>563154</v>
       </c>
       <c r="R33" t="n">
-        <v>7040216</v>
+        <v>7040221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,7 +4145,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,12 +4155,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4197,12 +4170,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4311,10 +4284,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233646</v>
+        <v>122234103</v>
       </c>
       <c r="B35" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4327,37 +4300,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562989</v>
+        <v>563089</v>
       </c>
       <c r="R35" t="n">
-        <v>7040172</v>
+        <v>7040216</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4384,9 +4362,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,19 +4394,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234000</v>
+        <v>122234038</v>
       </c>
       <c r="B36" t="n">
         <v>57379</v>
@@ -4458,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563097</v>
+        <v>563099</v>
       </c>
       <c r="R36" t="n">
-        <v>7040210</v>
+        <v>7040205</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4493,7 +4486,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4503,12 +4496,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,7 +4528,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234283</v>
+        <v>122234052</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -4571,7 +4564,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4580,10 +4573,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563202</v>
+        <v>563109</v>
       </c>
       <c r="R37" t="n">
-        <v>7040231</v>
+        <v>7040194</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4615,7 +4608,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4625,12 +4618,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,7 +4650,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233933</v>
+        <v>122234000</v>
       </c>
       <c r="B38" t="n">
         <v>57379</v>
@@ -4698,14 +4691,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563089</v>
+        <v>563097</v>
       </c>
       <c r="R38" t="n">
-        <v>7040225</v>
+        <v>7040210</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4730,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,12 +4740,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4779,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232402</v>
+        <v>122233646</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4795,42 +4788,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562786</v>
+        <v>562989</v>
       </c>
       <c r="R39" t="n">
-        <v>7040064</v>
+        <v>7040172</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4863,11 +4848,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4894,7 +4874,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233350</v>
+        <v>122233933</v>
       </c>
       <c r="B40" t="n">
         <v>57379</v>
@@ -4939,10 +4919,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562930</v>
+        <v>563089</v>
       </c>
       <c r="R40" t="n">
-        <v>7040221</v>
+        <v>7040225</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,7 +4954,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4984,12 +4964,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5004,22 +4984,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122232270</v>
+        <v>122234058</v>
       </c>
       <c r="B41" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5032,37 +5012,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562828</v>
+        <v>563095</v>
       </c>
       <c r="R41" t="n">
-        <v>7040062</v>
+        <v>7040206</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5089,9 +5074,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431113</v>
+        <v>122431232</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,39 +5459,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562981</v>
+        <v>563034</v>
       </c>
       <c r="R45" t="n">
-        <v>7040158</v>
+        <v>7040085</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5524,11 +5519,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5660,7 +5650,7 @@
         <v>122431200</v>
       </c>
       <c r="B47" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5759,10 +5749,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431232</v>
+        <v>122431459</v>
       </c>
       <c r="B48" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,34 +5765,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563034</v>
+        <v>563214</v>
       </c>
       <c r="R48" t="n">
-        <v>7040085</v>
+        <v>7040130</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5835,6 +5830,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,7 +5861,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431459</v>
+        <v>122431113</v>
       </c>
       <c r="B49" t="n">
         <v>57379</v>
@@ -5902,14 +5902,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563214</v>
+        <v>562981</v>
       </c>
       <c r="R49" t="n">
-        <v>7040130</v>
+        <v>7040158</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234125</v>
+        <v>122233997</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,42 +1721,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563092</v>
+        <v>563095</v>
       </c>
       <c r="R12" t="n">
-        <v>7040220</v>
+        <v>7040157</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,24 +1778,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233997</v>
+        <v>122234125</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,37 +1823,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563095</v>
+        <v>563092</v>
       </c>
       <c r="R13" t="n">
-        <v>7040157</v>
+        <v>7040220</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1900,9 +1885,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233647</v>
+        <v>122232285</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,42 +1945,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562988</v>
+        <v>562818</v>
       </c>
       <c r="R14" t="n">
-        <v>7040196</v>
+        <v>7040065</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2007,24 +2002,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122232285</v>
+        <v>122233647</v>
       </c>
       <c r="B15" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,37 +2047,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562818</v>
+        <v>562988</v>
       </c>
       <c r="R15" t="n">
-        <v>7040065</v>
+        <v>7040196</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,9 +2109,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122232285</v>
+        <v>122233647</v>
       </c>
       <c r="B14" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,37 +1945,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562818</v>
+        <v>562988</v>
       </c>
       <c r="R14" t="n">
-        <v>7040065</v>
+        <v>7040196</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,9 +2007,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2039,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233647</v>
+        <v>122232285</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,42 +2067,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562988</v>
+        <v>562818</v>
       </c>
       <c r="R15" t="n">
-        <v>7040196</v>
+        <v>7040065</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,24 +2124,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233127</v>
+        <v>122233673</v>
       </c>
       <c r="B11" t="n">
-        <v>79732</v>
+        <v>79769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1628,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562875</v>
+        <v>562986</v>
       </c>
       <c r="R11" t="n">
-        <v>7040276</v>
+        <v>7040156</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,19 +1661,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1678,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233997</v>
+        <v>122233217</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,11 +1708,6 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1745,13 +1725,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563095</v>
+        <v>562922</v>
       </c>
       <c r="R12" t="n">
-        <v>7040157</v>
+        <v>7040240</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,9 +1758,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234125</v>
+        <v>122233625</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,42 +1813,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563092</v>
+        <v>562978</v>
       </c>
       <c r="R13" t="n">
-        <v>7040220</v>
+        <v>7040170</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,24 +1865,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,19 +1882,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233647</v>
+        <v>122234058</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1947,11 +1912,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1965,19 +1925,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562988</v>
+        <v>563095</v>
       </c>
       <c r="R14" t="n">
-        <v>7040196</v>
+        <v>7040206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +1969,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2019,12 +1979,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122232285</v>
+        <v>122233647</v>
       </c>
       <c r="B15" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,37 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562818</v>
+        <v>562988</v>
       </c>
       <c r="R15" t="n">
-        <v>7040065</v>
+        <v>7040196</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,9 +2084,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233217</v>
+        <v>122234359</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>82439</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,31 +2144,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>1312</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562922</v>
+        <v>563205</v>
       </c>
       <c r="R16" t="n">
         <v>7040240</v>
@@ -2228,7 +2198,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2238,7 +2208,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122232184</v>
+        <v>122234194</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,11 +2253,6 @@
       <c r="E17" t="n">
         <v>6425</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2301,17 +2266,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562833</v>
+        <v>563154</v>
       </c>
       <c r="R17" t="n">
-        <v>7040085</v>
+        <v>7040221</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2303,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,19 +2330,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233350</v>
+        <v>122234125</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2385,11 +2360,6 @@
       <c r="E18" t="n">
         <v>100109</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2403,7 +2373,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2412,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562930</v>
+        <v>563092</v>
       </c>
       <c r="R18" t="n">
-        <v>7040221</v>
+        <v>7040220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2417,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,12 +2427,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,22 +2447,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122234176</v>
+        <v>122233994</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,39 +2475,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>563088</v>
       </c>
       <c r="R19" t="n">
-        <v>7040234</v>
+        <v>7040175</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2529,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,12 +2539,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,22 +2554,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233750</v>
+        <v>122232270</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,42 +2582,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563040</v>
+        <v>562828</v>
       </c>
       <c r="R20" t="n">
-        <v>7040180</v>
+        <v>7040062</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,24 +2634,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,19 +2651,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233260</v>
+        <v>122233350</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2751,11 +2681,6 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2778,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562896</v>
+        <v>562930</v>
       </c>
       <c r="R21" t="n">
-        <v>7040281</v>
+        <v>7040221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,7 +2738,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2823,12 +2748,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,22 +2768,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122233994</v>
+        <v>122232949</v>
       </c>
       <c r="B22" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,34 +2796,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563088</v>
+        <v>562836</v>
       </c>
       <c r="R22" t="n">
-        <v>7040175</v>
+        <v>7040209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2865,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,19 +2885,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122232402</v>
+        <v>122234283</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2985,11 +2915,6 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3001,27 +2926,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562786</v>
+        <v>563202</v>
       </c>
       <c r="R23" t="n">
-        <v>7040064</v>
+        <v>7040231</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3048,14 +2970,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3070,22 +3002,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122232469</v>
+        <v>122232285</v>
       </c>
       <c r="B24" t="n">
-        <v>90808</v>
+        <v>79733</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,21 +3030,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3122,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562748</v>
+        <v>562818</v>
       </c>
       <c r="R24" t="n">
-        <v>7040047</v>
+        <v>7040065</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3184,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122232495</v>
+        <v>122233260</v>
       </c>
       <c r="B25" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,37 +3127,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562748</v>
+        <v>562896</v>
       </c>
       <c r="R25" t="n">
-        <v>7040046</v>
+        <v>7040281</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3257,9 +3184,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,19 +3216,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122233345</v>
+        <v>122234052</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3304,11 +3246,6 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3327,14 +3264,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562904</v>
+        <v>563109</v>
       </c>
       <c r="R26" t="n">
-        <v>7040280</v>
+        <v>7040194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,12 +3313,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3396,22 +3333,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233673</v>
+        <v>122232932</v>
       </c>
       <c r="B27" t="n">
-        <v>79768</v>
+        <v>82439</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,25 +3357,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>1312</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3448,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562986</v>
+        <v>562795</v>
       </c>
       <c r="R27" t="n">
-        <v>7040156</v>
+        <v>7040090</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3510,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122234359</v>
+        <v>122232469</v>
       </c>
       <c r="B28" t="n">
-        <v>82438</v>
+        <v>90813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,37 +3458,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563205</v>
+        <v>562748</v>
       </c>
       <c r="R28" t="n">
-        <v>7040240</v>
+        <v>7040047</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3583,19 +3510,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3610,22 +3527,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232932</v>
+        <v>122234038</v>
       </c>
       <c r="B29" t="n">
-        <v>82438</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,37 +3555,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562795</v>
+        <v>563099</v>
       </c>
       <c r="R29" t="n">
-        <v>7040090</v>
+        <v>7040205</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3695,9 +3612,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,22 +3644,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232949</v>
+        <v>122233127</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,39 +3672,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562836</v>
+        <v>562875</v>
       </c>
       <c r="R30" t="n">
-        <v>7040209</v>
+        <v>7040276</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3804,7 +3726,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3814,12 +3736,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3846,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234283</v>
+        <v>122233750</v>
       </c>
       <c r="B31" t="n">
         <v>57379</v>
@@ -3864,11 +3781,6 @@
       <c r="E31" t="n">
         <v>100109</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3882,19 +3794,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563202</v>
+        <v>563040</v>
       </c>
       <c r="R31" t="n">
-        <v>7040231</v>
+        <v>7040180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3926,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3936,12 +3848,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122232270</v>
+        <v>122234103</v>
       </c>
       <c r="B32" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3984,37 +3896,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562828</v>
+        <v>563089</v>
       </c>
       <c r="R32" t="n">
-        <v>7040062</v>
+        <v>7040216</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4041,9 +3953,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,22 +3985,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122234194</v>
+        <v>122233933</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4086,34 +4013,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563154</v>
+        <v>563089</v>
       </c>
       <c r="R33" t="n">
-        <v>7040221</v>
+        <v>7040225</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,7 +4072,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4155,7 +4082,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4170,22 +4102,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233625</v>
+        <v>122234000</v>
       </c>
       <c r="B34" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4198,37 +4130,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562978</v>
+        <v>563097</v>
       </c>
       <c r="R34" t="n">
-        <v>7040170</v>
+        <v>7040210</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4255,9 +4187,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4272,22 +4219,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234103</v>
+        <v>122233646</v>
       </c>
       <c r="B35" t="n">
-        <v>57379</v>
+        <v>79734</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4300,42 +4247,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563089</v>
+        <v>562989</v>
       </c>
       <c r="R35" t="n">
-        <v>7040216</v>
+        <v>7040172</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4362,24 +4299,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4394,19 +4316,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234038</v>
+        <v>122233345</v>
       </c>
       <c r="B36" t="n">
         <v>57379</v>
@@ -4424,11 +4346,6 @@
       <c r="E36" t="n">
         <v>100109</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4447,14 +4364,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563099</v>
+        <v>562904</v>
       </c>
       <c r="R36" t="n">
-        <v>7040205</v>
+        <v>7040280</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4486,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4496,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4528,7 +4445,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234052</v>
+        <v>122232402</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -4546,11 +4463,6 @@
       <c r="E37" t="n">
         <v>100109</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4562,24 +4474,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563109</v>
+        <v>562786</v>
       </c>
       <c r="R37" t="n">
-        <v>7040194</v>
+        <v>7040064</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4606,24 +4521,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,19 +4543,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122234000</v>
+        <v>122234176</v>
       </c>
       <c r="B38" t="n">
         <v>57379</v>
@@ -4668,11 +4573,6 @@
       <c r="E38" t="n">
         <v>100109</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4686,7 +4586,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4695,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563097</v>
+        <v>563102</v>
       </c>
       <c r="R38" t="n">
-        <v>7040210</v>
+        <v>7040234</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4730,7 +4630,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4740,12 +4640,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233646</v>
+        <v>122233997</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4788,21 +4688,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4812,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562989</v>
+        <v>563095</v>
       </c>
       <c r="R39" t="n">
-        <v>7040172</v>
+        <v>7040157</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4874,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233933</v>
+        <v>122232184</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4890,42 +4785,32 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563089</v>
+        <v>562833</v>
       </c>
       <c r="R40" t="n">
-        <v>7040225</v>
+        <v>7040085</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4952,24 +4837,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +4854,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234058</v>
+        <v>122232495</v>
       </c>
       <c r="B41" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5012,42 +4882,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563095</v>
+        <v>562748</v>
       </c>
       <c r="R41" t="n">
-        <v>7040206</v>
+        <v>7040046</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5074,24 +4934,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +4951,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5121,7 +4966,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79598</v>
+        <v>79599</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5135,11 +4980,6 @@
       </c>
       <c r="E42" t="n">
         <v>388</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Stiftgelélav</t>
-        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5209,11 +5049,6 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
       <c r="AK42" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -5242,7 +5077,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5256,11 +5091,6 @@
       </c>
       <c r="E43" t="n">
         <v>6458</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5341,10 +5171,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431003</v>
+        <v>122431200</v>
       </c>
       <c r="B44" t="n">
-        <v>79732</v>
+        <v>90831</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,21 +5187,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5206,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562919</v>
+        <v>563033</v>
       </c>
       <c r="R44" t="n">
-        <v>7040173</v>
+        <v>7040085</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5443,10 +5268,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431232</v>
+        <v>122431459</v>
       </c>
       <c r="B45" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,34 +5284,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563034</v>
+        <v>563214</v>
       </c>
       <c r="R45" t="n">
-        <v>7040085</v>
+        <v>7040130</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5519,6 +5344,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5548,7 +5378,7 @@
         <v>122431528</v>
       </c>
       <c r="B46" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5562,11 +5392,6 @@
       </c>
       <c r="E46" t="n">
         <v>6425</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5647,10 +5472,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431200</v>
+        <v>122431232</v>
       </c>
       <c r="B47" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5663,21 +5488,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,7 +5507,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563033</v>
+        <v>563034</v>
       </c>
       <c r="R47" t="n">
         <v>7040085</v>
@@ -5749,7 +5569,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431459</v>
+        <v>122431113</v>
       </c>
       <c r="B48" t="n">
         <v>57379</v>
@@ -5767,11 +5587,6 @@
       <c r="E48" t="n">
         <v>100109</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5790,14 +5605,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563214</v>
+        <v>562981</v>
       </c>
       <c r="R48" t="n">
-        <v>7040130</v>
+        <v>7040158</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5834,7 +5649,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,10 +5676,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431113</v>
+        <v>122431003</v>
       </c>
       <c r="B49" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5877,39 +5692,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562981</v>
+        <v>562919</v>
       </c>
       <c r="R49" t="n">
-        <v>7040158</v>
+        <v>7040173</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5942,11 +5747,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -2663,7 +2663,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233350</v>
+        <v>122232949</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562930</v>
+        <v>562836</v>
       </c>
       <c r="R21" t="n">
-        <v>7040221</v>
+        <v>7040209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2768,19 +2768,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232949</v>
+        <v>122233350</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562836</v>
+        <v>562930</v>
       </c>
       <c r="R22" t="n">
-        <v>7040209</v>
+        <v>7040221</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,12 +2885,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233217</v>
+        <v>122234359</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>82439</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1706,26 +1706,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562922</v>
+        <v>563205</v>
       </c>
       <c r="R12" t="n">
         <v>7040240</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233625</v>
+        <v>122234058</v>
       </c>
       <c r="B13" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,32 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562978</v>
+        <v>563095</v>
       </c>
       <c r="R13" t="n">
-        <v>7040170</v>
+        <v>7040206</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,9 +1870,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,19 +1902,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122234058</v>
+        <v>122233647</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1925,19 +1945,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563095</v>
+        <v>562988</v>
       </c>
       <c r="R14" t="n">
-        <v>7040206</v>
+        <v>7040196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1989,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1979,12 +1999,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233647</v>
+        <v>122233217</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2047,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562988</v>
+        <v>562922</v>
       </c>
       <c r="R15" t="n">
-        <v>7040196</v>
+        <v>7040240</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2101,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,12 +2111,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122234359</v>
+        <v>122233625</v>
       </c>
       <c r="B16" t="n">
-        <v>82439</v>
+        <v>79733</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,32 +2154,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563205</v>
+        <v>562978</v>
       </c>
       <c r="R16" t="n">
-        <v>7040240</v>
+        <v>7040170</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2196,19 +2206,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,12 +2223,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122232469</v>
+        <v>122233127</v>
       </c>
       <c r="B28" t="n">
-        <v>90813</v>
+        <v>79733</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562748</v>
+        <v>562875</v>
       </c>
       <c r="R28" t="n">
-        <v>7040047</v>
+        <v>7040276</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3510,9 +3510,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3527,12 +3537,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3656,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233127</v>
+        <v>122232469</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>90813</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,16 +3682,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,13 +3701,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562875</v>
+        <v>562748</v>
       </c>
       <c r="R30" t="n">
-        <v>7040276</v>
+        <v>7040047</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3724,19 +3734,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,12 +3751,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233673</v>
+        <v>122234052</v>
       </c>
       <c r="B11" t="n">
-        <v>79769</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,36 +1605,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562986</v>
+        <v>563109</v>
       </c>
       <c r="R11" t="n">
-        <v>7040156</v>
+        <v>7040194</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1661,9 +1671,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234359</v>
+        <v>122232270</v>
       </c>
       <c r="B12" t="n">
-        <v>82439</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1706,32 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563205</v>
+        <v>562828</v>
       </c>
       <c r="R12" t="n">
-        <v>7040240</v>
+        <v>7040062</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1758,19 +1788,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234058</v>
+        <v>122233647</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,6 +1835,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1828,19 +1853,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563095</v>
+        <v>562988</v>
       </c>
       <c r="R13" t="n">
-        <v>7040206</v>
+        <v>7040196</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,7 +1897,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1882,12 +1907,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233647</v>
+        <v>122232949</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,6 +1957,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1954,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562988</v>
+        <v>562836</v>
       </c>
       <c r="R14" t="n">
-        <v>7040196</v>
+        <v>7040209</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1999,12 +2029,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2049,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233217</v>
+        <v>122233345</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,29 +2077,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562922</v>
+        <v>562904</v>
       </c>
       <c r="R15" t="n">
-        <v>7040240</v>
+        <v>7040280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2111,7 +2151,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,22 +2171,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233625</v>
+        <v>122232402</v>
       </c>
       <c r="B16" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,29 +2199,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562978</v>
+        <v>562786</v>
       </c>
       <c r="R16" t="n">
-        <v>7040170</v>
+        <v>7040064</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2209,6 +2267,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122234194</v>
+        <v>122234176</v>
       </c>
       <c r="B17" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,29 +2314,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563154</v>
+        <v>563102</v>
       </c>
       <c r="R17" t="n">
-        <v>7040221</v>
+        <v>7040234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2378,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2388,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,22 +2408,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122234125</v>
+        <v>122233127</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,34 +2436,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563092</v>
+        <v>562875</v>
       </c>
       <c r="R18" t="n">
-        <v>7040220</v>
+        <v>7040276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2495,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2427,12 +2505,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233994</v>
+        <v>122233260</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,29 +2548,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563088</v>
+        <v>562896</v>
       </c>
       <c r="R19" t="n">
-        <v>7040175</v>
+        <v>7040281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2612,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2539,7 +2622,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2554,22 +2642,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232270</v>
+        <v>122233997</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,16 +2670,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562828</v>
+        <v>563095</v>
       </c>
       <c r="R20" t="n">
-        <v>7040062</v>
+        <v>7040157</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2663,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122232949</v>
+        <v>122233217</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,34 +2772,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562836</v>
+        <v>562922</v>
       </c>
       <c r="R21" t="n">
-        <v>7040209</v>
+        <v>7040240</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2831,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2748,12 +2841,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2768,22 +2856,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122233350</v>
+        <v>122232285</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,37 +2884,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562930</v>
+        <v>562818</v>
       </c>
       <c r="R22" t="n">
-        <v>7040221</v>
+        <v>7040065</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2853,24 +2941,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,22 +2958,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122234283</v>
+        <v>122233750</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,6 +2988,11 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2928,19 +3006,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563202</v>
+        <v>563040</v>
       </c>
       <c r="R23" t="n">
-        <v>7040231</v>
+        <v>7040180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2982,12 +3060,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3092,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122232285</v>
+        <v>122233933</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,32 +3108,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562818</v>
+        <v>563089</v>
       </c>
       <c r="R24" t="n">
-        <v>7040065</v>
+        <v>7040225</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3082,9 +3170,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3099,22 +3202,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233260</v>
+        <v>122234359</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>82443</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,34 +3230,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562896</v>
+        <v>563205</v>
       </c>
       <c r="R25" t="n">
-        <v>7040281</v>
+        <v>7040240</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3196,12 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,22 +3314,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234052</v>
+        <v>122232495</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,37 +3342,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563109</v>
+        <v>562748</v>
       </c>
       <c r="R26" t="n">
-        <v>7040194</v>
+        <v>7040046</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3301,24 +3399,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,22 +3416,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122232932</v>
+        <v>122233350</v>
       </c>
       <c r="B27" t="n">
-        <v>82439</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,32 +3444,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562795</v>
+        <v>562930</v>
       </c>
       <c r="R27" t="n">
-        <v>7040090</v>
+        <v>7040221</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3413,9 +3506,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,22 +3538,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233127</v>
+        <v>122234038</v>
       </c>
       <c r="B28" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,29 +3566,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562875</v>
+        <v>563099</v>
       </c>
       <c r="R28" t="n">
-        <v>7040276</v>
+        <v>7040205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3630,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3522,7 +3640,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234038</v>
+        <v>122233646</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>79738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,37 +3688,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2081</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563099</v>
+        <v>562989</v>
       </c>
       <c r="R29" t="n">
-        <v>7040205</v>
+        <v>7040172</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3622,24 +3745,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,22 +3762,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232469</v>
+        <v>122234000</v>
       </c>
       <c r="B30" t="n">
-        <v>90813</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,32 +3790,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562748</v>
+        <v>563097</v>
       </c>
       <c r="R30" t="n">
-        <v>7040047</v>
+        <v>7040210</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3734,9 +3852,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,22 +3884,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122233750</v>
+        <v>122234058</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3781,6 +3914,11 @@
       <c r="E31" t="n">
         <v>100109</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3794,19 +3932,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563040</v>
+        <v>563095</v>
       </c>
       <c r="R31" t="n">
-        <v>7040180</v>
+        <v>7040206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3976,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,12 +3986,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3868,22 +4006,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234103</v>
+        <v>122234194</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3896,34 +4034,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563089</v>
+        <v>563154</v>
       </c>
       <c r="R32" t="n">
-        <v>7040216</v>
+        <v>7040221</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,12 +4103,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3985,22 +4118,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233933</v>
+        <v>122233994</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4013,34 +4146,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563089</v>
+        <v>563088</v>
       </c>
       <c r="R33" t="n">
-        <v>7040225</v>
+        <v>7040175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4082,12 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,22 +4230,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122234000</v>
+        <v>122233673</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>79773</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4126,41 +4254,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6464</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563097</v>
+        <v>562986</v>
       </c>
       <c r="R34" t="n">
-        <v>7040210</v>
+        <v>7040156</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,24 +4315,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,22 +4332,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233646</v>
+        <v>122232469</v>
       </c>
       <c r="B35" t="n">
-        <v>79734</v>
+        <v>90826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4247,16 +4360,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4266,10 +4384,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562989</v>
+        <v>562748</v>
       </c>
       <c r="R35" t="n">
-        <v>7040172</v>
+        <v>7040047</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4328,10 +4446,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122233345</v>
+        <v>122232184</v>
       </c>
       <c r="B36" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4344,37 +4462,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562904</v>
+        <v>562833</v>
       </c>
       <c r="R36" t="n">
-        <v>7040280</v>
+        <v>7040085</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4401,24 +4519,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,22 +4536,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122232402</v>
+        <v>122234103</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,6 +4566,11 @@
       <c r="E37" t="n">
         <v>100109</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4474,27 +4582,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562786</v>
+        <v>563089</v>
       </c>
       <c r="R37" t="n">
-        <v>7040064</v>
+        <v>7040216</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4521,14 +4626,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4543,22 +4658,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122234176</v>
+        <v>122234283</v>
       </c>
       <c r="B38" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4573,6 +4688,11 @@
       <c r="E38" t="n">
         <v>100109</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4595,10 +4715,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563102</v>
+        <v>563202</v>
       </c>
       <c r="R38" t="n">
-        <v>7040234</v>
+        <v>7040231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,7 +4750,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4640,12 +4760,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4660,22 +4780,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233997</v>
+        <v>122233625</v>
       </c>
       <c r="B39" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4688,16 +4808,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4832,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563095</v>
+        <v>562978</v>
       </c>
       <c r="R39" t="n">
-        <v>7040157</v>
+        <v>7040170</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4769,10 +4894,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122232184</v>
+        <v>122232932</v>
       </c>
       <c r="B40" t="n">
-        <v>78652</v>
+        <v>82443</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4785,16 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4934,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562833</v>
+        <v>562795</v>
       </c>
       <c r="R40" t="n">
-        <v>7040085</v>
+        <v>7040090</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4866,10 +4996,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122232495</v>
+        <v>122234125</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4882,32 +5012,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562748</v>
+        <v>563092</v>
       </c>
       <c r="R41" t="n">
-        <v>7040046</v>
+        <v>7040220</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4934,9 +5074,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4951,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4966,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79599</v>
+        <v>79603</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4980,6 +5135,11 @@
       </c>
       <c r="E42" t="n">
         <v>388</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5049,6 +5209,11 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
       <c r="AK42" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -5077,7 +5242,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5091,6 +5256,11 @@
       </c>
       <c r="E43" t="n">
         <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5171,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431200</v>
+        <v>122431232</v>
       </c>
       <c r="B44" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5187,16 +5357,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5206,7 +5381,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563033</v>
+        <v>563034</v>
       </c>
       <c r="R44" t="n">
         <v>7040085</v>
@@ -5268,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431459</v>
+        <v>122431003</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5284,34 +5459,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563214</v>
+        <v>562919</v>
       </c>
       <c r="R45" t="n">
-        <v>7040130</v>
+        <v>7040173</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5344,11 +5519,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5375,10 +5545,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431528</v>
+        <v>122431200</v>
       </c>
       <c r="B46" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5391,29 +5561,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563173</v>
+        <v>563033</v>
       </c>
       <c r="R46" t="n">
-        <v>7040184</v>
+        <v>7040085</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5472,10 +5647,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431232</v>
+        <v>122431113</v>
       </c>
       <c r="B47" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5488,29 +5663,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563034</v>
+        <v>562981</v>
       </c>
       <c r="R47" t="n">
-        <v>7040085</v>
+        <v>7040158</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5543,6 +5728,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5569,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431113</v>
+        <v>122431528</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5585,34 +5775,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562981</v>
+        <v>563173</v>
       </c>
       <c r="R48" t="n">
-        <v>7040158</v>
+        <v>7040184</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5645,11 +5835,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5676,10 +5861,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431003</v>
+        <v>122431459</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5692,29 +5877,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562919</v>
+        <v>563214</v>
       </c>
       <c r="R49" t="n">
-        <v>7040173</v>
+        <v>7040130</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5747,6 +5942,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234052</v>
+        <v>122232469</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563109</v>
+        <v>562748</v>
       </c>
       <c r="R11" t="n">
-        <v>7040194</v>
+        <v>7040047</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,24 +1666,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122232270</v>
+        <v>122234000</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,37 +1711,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562828</v>
+        <v>563097</v>
       </c>
       <c r="R12" t="n">
-        <v>7040062</v>
+        <v>7040210</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,9 +1773,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,19 +1805,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233647</v>
+        <v>122233933</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562988</v>
+        <v>563089</v>
       </c>
       <c r="R13" t="n">
-        <v>7040196</v>
+        <v>7040225</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,19 +1927,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122232949</v>
+        <v>122233350</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562836</v>
+        <v>562930</v>
       </c>
       <c r="R14" t="n">
-        <v>7040209</v>
+        <v>7040221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,19 +2049,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233345</v>
+        <v>122234176</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2097,19 +2097,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562904</v>
+        <v>563102</v>
       </c>
       <c r="R15" t="n">
-        <v>7040280</v>
+        <v>7040234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122232402</v>
+        <v>122234052</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2217,27 +2217,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562786</v>
+        <v>563109</v>
       </c>
       <c r="R16" t="n">
-        <v>7040064</v>
+        <v>7040194</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,14 +2261,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,22 +2293,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122234176</v>
+        <v>122233997</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,42 +2321,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563102</v>
+        <v>563095</v>
       </c>
       <c r="R17" t="n">
-        <v>7040234</v>
+        <v>7040157</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,24 +2378,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,22 +2395,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233127</v>
+        <v>122234125</v>
       </c>
       <c r="B18" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2436,34 +2423,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562875</v>
+        <v>563092</v>
       </c>
       <c r="R18" t="n">
-        <v>7040276</v>
+        <v>7040220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2505,7 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122233260</v>
+        <v>122234359</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,39 +2545,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562896</v>
+        <v>563205</v>
       </c>
       <c r="R19" t="n">
-        <v>7040281</v>
+        <v>7040240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,12 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,22 +2629,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233997</v>
+        <v>122232495</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2670,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2694,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563095</v>
+        <v>562748</v>
       </c>
       <c r="R20" t="n">
-        <v>7040157</v>
+        <v>7040046</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2756,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233217</v>
+        <v>122233625</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2759,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,13 +2783,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562922</v>
+        <v>562978</v>
       </c>
       <c r="R21" t="n">
-        <v>7040240</v>
+        <v>7040170</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2829,19 +2816,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,22 +2833,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232285</v>
+        <v>122232949</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2884,37 +2861,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562818</v>
+        <v>562836</v>
       </c>
       <c r="R22" t="n">
-        <v>7040065</v>
+        <v>7040209</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2941,9 +2923,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,22 +2955,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233750</v>
+        <v>122233673</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>79773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2982,46 +2979,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563040</v>
+        <v>562986</v>
       </c>
       <c r="R23" t="n">
-        <v>7040180</v>
+        <v>7040156</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3048,24 +3040,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,19 +3057,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233933</v>
+        <v>122234038</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3133,14 +3110,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563089</v>
+        <v>563099</v>
       </c>
       <c r="R24" t="n">
-        <v>7040225</v>
+        <v>7040205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,7 +3149,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3182,12 +3159,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,10 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122234359</v>
+        <v>122233127</v>
       </c>
       <c r="B25" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,34 +3207,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563205</v>
+        <v>562875</v>
       </c>
       <c r="R25" t="n">
-        <v>7040240</v>
+        <v>7040276</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,22 +3291,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232495</v>
+        <v>122234058</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3342,37 +3319,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562748</v>
+        <v>563095</v>
       </c>
       <c r="R26" t="n">
-        <v>7040046</v>
+        <v>7040206</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3399,9 +3381,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,19 +3413,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233350</v>
+        <v>122233345</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3473,10 +3470,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562930</v>
+        <v>562904</v>
       </c>
       <c r="R27" t="n">
-        <v>7040221</v>
+        <v>7040280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3508,7 +3505,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3518,12 +3515,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,19 +3535,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122234038</v>
+        <v>122232402</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3584,24 +3581,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563099</v>
+        <v>562786</v>
       </c>
       <c r="R28" t="n">
-        <v>7040205</v>
+        <v>7040064</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,24 +3628,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,22 +3650,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122233646</v>
+        <v>122233750</v>
       </c>
       <c r="B29" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,37 +3678,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562989</v>
+        <v>563040</v>
       </c>
       <c r="R29" t="n">
-        <v>7040172</v>
+        <v>7040180</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3745,9 +3740,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,19 +3772,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122234000</v>
+        <v>122233647</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3815,14 +3825,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563097</v>
+        <v>562988</v>
       </c>
       <c r="R30" t="n">
-        <v>7040210</v>
+        <v>7040196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3854,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3864,12 +3874,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3884,19 +3894,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234058</v>
+        <v>122234103</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -3932,19 +3942,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563095</v>
+        <v>563089</v>
       </c>
       <c r="R31" t="n">
-        <v>7040206</v>
+        <v>7040216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,7 +3986,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3986,7 +3996,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4018,7 +4028,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122234194</v>
+        <v>122233994</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -4054,14 +4064,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563154</v>
+        <v>563088</v>
       </c>
       <c r="R32" t="n">
-        <v>7040221</v>
+        <v>7040175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4093,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4103,7 +4113,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233994</v>
+        <v>122233646</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4146,21 +4156,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,13 +4180,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563088</v>
+        <v>562989</v>
       </c>
       <c r="R33" t="n">
-        <v>7040175</v>
+        <v>7040172</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4203,19 +4213,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4230,22 +4230,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233673</v>
+        <v>122232932</v>
       </c>
       <c r="B34" t="n">
-        <v>79773</v>
+        <v>82443</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4254,25 +4254,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562986</v>
+        <v>562795</v>
       </c>
       <c r="R34" t="n">
-        <v>7040156</v>
+        <v>7040090</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122232469</v>
+        <v>122234194</v>
       </c>
       <c r="B35" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,37 +4360,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562748</v>
+        <v>563154</v>
       </c>
       <c r="R35" t="n">
-        <v>7040047</v>
+        <v>7040221</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4417,9 +4417,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4434,12 +4444,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4548,7 +4558,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234103</v>
+        <v>122234283</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -4584,19 +4594,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563089</v>
+        <v>563202</v>
       </c>
       <c r="R37" t="n">
-        <v>7040216</v>
+        <v>7040231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4628,7 +4638,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4638,12 +4648,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,22 +4668,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122234283</v>
+        <v>122232285</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4686,42 +4696,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563202</v>
+        <v>562818</v>
       </c>
       <c r="R38" t="n">
-        <v>7040231</v>
+        <v>7040065</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4748,24 +4753,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,22 +4770,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233625</v>
+        <v>122233217</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4808,21 +4798,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4832,13 +4822,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562978</v>
+        <v>562922</v>
       </c>
       <c r="R39" t="n">
-        <v>7040170</v>
+        <v>7040240</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4865,9 +4855,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,22 +4882,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122232932</v>
+        <v>122233260</v>
       </c>
       <c r="B40" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,37 +4910,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562795</v>
+        <v>562896</v>
       </c>
       <c r="R40" t="n">
-        <v>7040090</v>
+        <v>7040281</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,9 +4972,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +5004,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234125</v>
+        <v>122232270</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5012,42 +5032,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563092</v>
+        <v>562828</v>
       </c>
       <c r="R41" t="n">
-        <v>7040220</v>
+        <v>7040062</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5074,24 +5089,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431232</v>
+        <v>122431528</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5377,14 +5377,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563034</v>
+        <v>563173</v>
       </c>
       <c r="R44" t="n">
-        <v>7040085</v>
+        <v>7040184</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431003</v>
+        <v>122431232</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562919</v>
+        <v>563034</v>
       </c>
       <c r="R45" t="n">
-        <v>7040173</v>
+        <v>7040085</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431200</v>
+        <v>122431003</v>
       </c>
       <c r="B46" t="n">
-        <v>90844</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563033</v>
+        <v>562919</v>
       </c>
       <c r="R46" t="n">
-        <v>7040085</v>
+        <v>7040173</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431113</v>
+        <v>122431459</v>
       </c>
       <c r="B47" t="n">
         <v>57383</v>
@@ -5688,14 +5688,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562981</v>
+        <v>563214</v>
       </c>
       <c r="R47" t="n">
-        <v>7040158</v>
+        <v>7040130</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431528</v>
+        <v>122431200</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,34 +5775,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563173</v>
+        <v>563033</v>
       </c>
       <c r="R48" t="n">
-        <v>7040184</v>
+        <v>7040085</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431459</v>
+        <v>122431113</v>
       </c>
       <c r="B49" t="n">
         <v>57383</v>
@@ -5902,14 +5902,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563214</v>
+        <v>562981</v>
       </c>
       <c r="R49" t="n">
-        <v>7040130</v>
+        <v>7040158</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122232469</v>
+        <v>122234000</v>
       </c>
       <c r="B11" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1609,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562748</v>
+        <v>563097</v>
       </c>
       <c r="R11" t="n">
-        <v>7040047</v>
+        <v>7040210</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1671,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,19 +1703,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234000</v>
+        <v>122233933</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1736,14 +1756,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563097</v>
+        <v>563089</v>
       </c>
       <c r="R12" t="n">
-        <v>7040210</v>
+        <v>7040225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1785,12 +1805,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122233933</v>
+        <v>122232469</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,42 +1853,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563089</v>
+        <v>562748</v>
       </c>
       <c r="R13" t="n">
-        <v>7040225</v>
+        <v>7040047</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1895,24 +1910,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122234125</v>
+        <v>122234359</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563092</v>
+        <v>563205</v>
       </c>
       <c r="R18" t="n">
-        <v>7040220</v>
+        <v>7040240</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,12 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,22 +2507,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122234359</v>
+        <v>122234125</v>
       </c>
       <c r="B19" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2545,34 +2535,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563205</v>
+        <v>563092</v>
       </c>
       <c r="R19" t="n">
-        <v>7040240</v>
+        <v>7040220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,12 +2629,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234000</v>
+        <v>122233997</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563097</v>
+        <v>563095</v>
       </c>
       <c r="R11" t="n">
-        <v>7040210</v>
+        <v>7040157</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,24 +1666,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,19 +1683,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233933</v>
+        <v>122234103</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1763,7 +1743,7 @@
         <v>563089</v>
       </c>
       <c r="R12" t="n">
-        <v>7040225</v>
+        <v>7040216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1775,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1805,12 +1785,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på stående gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122232469</v>
+        <v>122234283</v>
       </c>
       <c r="B13" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,37 +1833,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562748</v>
+        <v>563202</v>
       </c>
       <c r="R13" t="n">
-        <v>7040047</v>
+        <v>7040231</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,9 +1895,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,22 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233350</v>
+        <v>122232495</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,42 +1955,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562930</v>
+        <v>562748</v>
       </c>
       <c r="R14" t="n">
-        <v>7040221</v>
+        <v>7040046</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,24 +2012,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,19 +2029,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234176</v>
+        <v>122233350</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2097,19 +2077,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563102</v>
+        <v>562930</v>
       </c>
       <c r="R15" t="n">
-        <v>7040234</v>
+        <v>7040221</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2121,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,12 +2131,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,19 +2151,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122234052</v>
+        <v>122233750</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2224,14 +2204,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563109</v>
+        <v>563040</v>
       </c>
       <c r="R16" t="n">
-        <v>7040194</v>
+        <v>7040180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,12 +2253,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233997</v>
+        <v>122233345</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,37 +2301,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563095</v>
+        <v>562904</v>
       </c>
       <c r="R17" t="n">
-        <v>7040157</v>
+        <v>7040280</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2378,9 +2363,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,22 +2395,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122234359</v>
+        <v>122233994</v>
       </c>
       <c r="B18" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,34 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563205</v>
+        <v>563088</v>
       </c>
       <c r="R18" t="n">
-        <v>7040240</v>
+        <v>7040175</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122234125</v>
+        <v>122232270</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,42 +2535,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563092</v>
+        <v>562828</v>
       </c>
       <c r="R19" t="n">
-        <v>7040220</v>
+        <v>7040062</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,24 +2592,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2609,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232495</v>
+        <v>122232402</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,34 +2637,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562748</v>
+        <v>562786</v>
       </c>
       <c r="R20" t="n">
-        <v>7040046</v>
+        <v>7040064</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2717,6 +2705,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233625</v>
+        <v>122234359</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,37 +2752,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562978</v>
+        <v>563205</v>
       </c>
       <c r="R21" t="n">
-        <v>7040170</v>
+        <v>7040240</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,9 +2809,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,22 +2836,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232949</v>
+        <v>122232184</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,42 +2864,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562836</v>
+        <v>562833</v>
       </c>
       <c r="R22" t="n">
-        <v>7040209</v>
+        <v>7040085</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2923,24 +2921,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233673</v>
+        <v>122233625</v>
       </c>
       <c r="B23" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,25 +2962,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3007,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562986</v>
+        <v>562978</v>
       </c>
       <c r="R23" t="n">
-        <v>7040156</v>
+        <v>7040170</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3069,7 +3052,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234038</v>
+        <v>122234058</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3105,7 +3088,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563099</v>
+        <v>563095</v>
       </c>
       <c r="R24" t="n">
-        <v>7040205</v>
+        <v>7040206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,7 +3132,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3159,7 +3142,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3191,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233127</v>
+        <v>122233646</v>
       </c>
       <c r="B25" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,21 +3190,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3231,13 +3214,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562875</v>
+        <v>562989</v>
       </c>
       <c r="R25" t="n">
-        <v>7040276</v>
+        <v>7040172</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3264,19 +3247,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,19 +3264,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234058</v>
+        <v>122232949</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3339,19 +3312,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563095</v>
+        <v>562836</v>
       </c>
       <c r="R26" t="n">
-        <v>7040206</v>
+        <v>7040209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,7 +3356,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,12 +3366,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3425,7 +3398,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233345</v>
+        <v>122234038</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3466,14 +3439,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562904</v>
+        <v>563099</v>
       </c>
       <c r="R27" t="n">
-        <v>7040280</v>
+        <v>7040205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3505,7 +3478,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3515,7 +3488,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3547,7 +3520,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122232402</v>
+        <v>122234176</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3581,27 +3554,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562786</v>
+        <v>563102</v>
       </c>
       <c r="R28" t="n">
-        <v>7040064</v>
+        <v>7040234</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,14 +3598,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,22 +3630,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122233750</v>
+        <v>122233217</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,39 +3658,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563040</v>
+        <v>562922</v>
       </c>
       <c r="R29" t="n">
-        <v>7040180</v>
+        <v>7040240</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3742,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3752,12 +3727,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3784,7 +3754,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233647</v>
+        <v>122234125</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3820,7 +3790,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3829,10 +3799,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562988</v>
+        <v>563092</v>
       </c>
       <c r="R30" t="n">
-        <v>7040196</v>
+        <v>7040220</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,7 +3834,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,12 +3844,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3894,19 +3864,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122234103</v>
+        <v>122233647</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -3951,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563089</v>
+        <v>562988</v>
       </c>
       <c r="R31" t="n">
-        <v>7040216</v>
+        <v>7040196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3986,7 +3956,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3996,12 +3966,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,22 +3986,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122233994</v>
+        <v>122232469</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4044,21 +4014,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4068,13 +4038,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563088</v>
+        <v>562748</v>
       </c>
       <c r="R32" t="n">
-        <v>7040175</v>
+        <v>7040047</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4101,19 +4071,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233646</v>
+        <v>122233260</v>
       </c>
       <c r="B33" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4156,37 +4116,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562989</v>
+        <v>562896</v>
       </c>
       <c r="R33" t="n">
-        <v>7040172</v>
+        <v>7040281</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,9 +4178,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4230,22 +4210,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122232932</v>
+        <v>122233933</v>
       </c>
       <c r="B34" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4258,37 +4238,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562795</v>
+        <v>563089</v>
       </c>
       <c r="R34" t="n">
-        <v>7040090</v>
+        <v>7040225</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4315,9 +4300,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,22 +4332,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234194</v>
+        <v>122233127</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563154</v>
+        <v>562875</v>
       </c>
       <c r="R35" t="n">
-        <v>7040221</v>
+        <v>7040276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,22 +4444,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122232184</v>
+        <v>122233673</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>79773</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,25 +4468,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562833</v>
+        <v>562986</v>
       </c>
       <c r="R36" t="n">
-        <v>7040085</v>
+        <v>7040156</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122234283</v>
+        <v>122232285</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4574,42 +4574,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563202</v>
+        <v>562818</v>
       </c>
       <c r="R37" t="n">
-        <v>7040231</v>
+        <v>7040065</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4636,24 +4631,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4668,22 +4648,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122232285</v>
+        <v>122232932</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,21 +4676,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,10 +4700,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562818</v>
+        <v>562795</v>
       </c>
       <c r="R38" t="n">
-        <v>7040065</v>
+        <v>7040090</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4782,10 +4762,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233217</v>
+        <v>122234000</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,34 +4778,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562922</v>
+        <v>563097</v>
       </c>
       <c r="R39" t="n">
-        <v>7040240</v>
+        <v>7040210</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4857,7 +4842,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4867,7 +4852,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,22 +4872,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233260</v>
+        <v>122234194</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,39 +4900,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562896</v>
+        <v>563154</v>
       </c>
       <c r="R40" t="n">
-        <v>7040281</v>
+        <v>7040221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4984,12 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5004,22 +4984,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122232270</v>
+        <v>122234052</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5032,37 +5012,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562828</v>
+        <v>563109</v>
       </c>
       <c r="R41" t="n">
-        <v>7040062</v>
+        <v>7040194</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5089,9 +5074,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431232</v>
+        <v>122431113</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,34 +5459,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563034</v>
+        <v>562981</v>
       </c>
       <c r="R45" t="n">
-        <v>7040085</v>
+        <v>7040158</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5519,6 +5524,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431003</v>
+        <v>122431200</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>90857</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5561,21 +5571,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,10 +5595,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562919</v>
+        <v>563033</v>
       </c>
       <c r="R46" t="n">
-        <v>7040173</v>
+        <v>7040085</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5759,10 +5769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431200</v>
+        <v>122431232</v>
       </c>
       <c r="B48" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,21 +5785,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5799,7 +5809,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563033</v>
+        <v>563034</v>
       </c>
       <c r="R48" t="n">
         <v>7040085</v>
@@ -5861,10 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431113</v>
+        <v>122431003</v>
       </c>
       <c r="B49" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5877,39 +5887,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562981</v>
+        <v>562919</v>
       </c>
       <c r="R49" t="n">
-        <v>7040158</v>
+        <v>7040173</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5942,11 +5947,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122233625</v>
+        <v>122234058</v>
       </c>
       <c r="B23" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,37 +2966,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562978</v>
+        <v>563095</v>
       </c>
       <c r="R23" t="n">
-        <v>7040170</v>
+        <v>7040206</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,9 +3028,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,22 +3060,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234058</v>
+        <v>122233625</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3068,42 +3088,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563095</v>
+        <v>562978</v>
       </c>
       <c r="R24" t="n">
-        <v>7040206</v>
+        <v>7040170</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3130,24 +3145,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,22 +3162,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233646</v>
+        <v>122232949</v>
       </c>
       <c r="B25" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3190,37 +3190,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562989</v>
+        <v>562836</v>
       </c>
       <c r="R25" t="n">
-        <v>7040172</v>
+        <v>7040209</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3247,9 +3252,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,19 +3284,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122232949</v>
+        <v>122234038</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3317,14 +3337,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562836</v>
+        <v>563099</v>
       </c>
       <c r="R26" t="n">
-        <v>7040209</v>
+        <v>7040205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3376,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3366,12 +3386,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,10 +3418,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122234038</v>
+        <v>122233646</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3414,42 +3434,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563099</v>
+        <v>562989</v>
       </c>
       <c r="R27" t="n">
-        <v>7040205</v>
+        <v>7040172</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3476,24 +3491,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,12 +3508,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122232469</v>
+        <v>122233260</v>
       </c>
       <c r="B32" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,37 +4014,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562748</v>
+        <v>562896</v>
       </c>
       <c r="R32" t="n">
-        <v>7040047</v>
+        <v>7040281</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4071,9 +4076,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4108,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233260</v>
+        <v>122232469</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4116,42 +4136,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562896</v>
+        <v>562748</v>
       </c>
       <c r="R33" t="n">
-        <v>7040281</v>
+        <v>7040047</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4178,24 +4193,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,12 +4210,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122233127</v>
+        <v>122232932</v>
       </c>
       <c r="B35" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562875</v>
+        <v>562795</v>
       </c>
       <c r="R35" t="n">
-        <v>7040276</v>
+        <v>7040090</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4417,19 +4417,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,22 +4434,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122233673</v>
+        <v>122233127</v>
       </c>
       <c r="B36" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,25 +4458,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,13 +4486,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562986</v>
+        <v>562875</v>
       </c>
       <c r="R36" t="n">
-        <v>7040156</v>
+        <v>7040276</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4529,9 +4519,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,22 +4546,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122232285</v>
+        <v>122233673</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,25 +4570,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562818</v>
+        <v>562986</v>
       </c>
       <c r="R37" t="n">
-        <v>7040065</v>
+        <v>7040156</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122232932</v>
+        <v>122232285</v>
       </c>
       <c r="B38" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562795</v>
+        <v>562818</v>
       </c>
       <c r="R38" t="n">
-        <v>7040090</v>
+        <v>7040065</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233997</v>
+        <v>122233933</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1609,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563095</v>
+        <v>563089</v>
       </c>
       <c r="R11" t="n">
-        <v>7040157</v>
+        <v>7040225</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1671,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,19 +1703,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122234103</v>
+        <v>122233345</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1740,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563089</v>
+        <v>562904</v>
       </c>
       <c r="R12" t="n">
-        <v>7040216</v>
+        <v>7040280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1785,7 +1805,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1817,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234283</v>
+        <v>122234125</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1858,14 +1878,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563202</v>
+        <v>563092</v>
       </c>
       <c r="R13" t="n">
-        <v>7040231</v>
+        <v>7040220</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1907,12 +1927,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,22 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122232495</v>
+        <v>122233646</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562748</v>
+        <v>562989</v>
       </c>
       <c r="R14" t="n">
-        <v>7040046</v>
+        <v>7040172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2041,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233350</v>
+        <v>122234194</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,36 +2077,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562930</v>
+        <v>563154</v>
       </c>
       <c r="R15" t="n">
         <v>7040221</v>
@@ -2121,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2131,12 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233750</v>
+        <v>122233625</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,42 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563040</v>
+        <v>562978</v>
       </c>
       <c r="R16" t="n">
-        <v>7040180</v>
+        <v>7040170</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,24 +2246,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,19 +2263,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233345</v>
+        <v>122233647</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562904</v>
+        <v>562988</v>
       </c>
       <c r="R17" t="n">
-        <v>7040280</v>
+        <v>7040196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,12 +2365,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,22 +2385,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233994</v>
+        <v>122233350</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,34 +2413,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563088</v>
+        <v>562930</v>
       </c>
       <c r="R18" t="n">
-        <v>7040175</v>
+        <v>7040221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2487,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122232270</v>
+        <v>122232469</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562828</v>
+        <v>562748</v>
       </c>
       <c r="R19" t="n">
-        <v>7040062</v>
+        <v>7040047</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232402</v>
+        <v>122232495</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,42 +2637,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562786</v>
+        <v>562748</v>
       </c>
       <c r="R20" t="n">
-        <v>7040064</v>
+        <v>7040046</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2705,11 +2697,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122234359</v>
+        <v>122233750</v>
       </c>
       <c r="B21" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2752,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563205</v>
+        <v>563040</v>
       </c>
       <c r="R21" t="n">
-        <v>7040240</v>
+        <v>7040180</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,7 +2813,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122232184</v>
+        <v>122234283</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2864,37 +2861,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562833</v>
+        <v>563202</v>
       </c>
       <c r="R22" t="n">
-        <v>7040085</v>
+        <v>7040231</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2921,9 +2923,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,12 +2955,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3072,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122233625</v>
+        <v>122234359</v>
       </c>
       <c r="B24" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3088,37 +3105,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562978</v>
+        <v>563205</v>
       </c>
       <c r="R24" t="n">
-        <v>7040170</v>
+        <v>7040240</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3145,9 +3162,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,22 +3189,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122232949</v>
+        <v>122233673</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>79773</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,46 +3213,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562836</v>
+        <v>562986</v>
       </c>
       <c r="R25" t="n">
-        <v>7040209</v>
+        <v>7040156</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3252,24 +3274,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,19 +3291,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234038</v>
+        <v>122234103</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3337,14 +3344,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563099</v>
+        <v>563089</v>
       </c>
       <c r="R26" t="n">
-        <v>7040205</v>
+        <v>7040216</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,7 +3383,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3386,7 +3393,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3418,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122233646</v>
+        <v>122234000</v>
       </c>
       <c r="B27" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3434,37 +3441,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562989</v>
+        <v>563097</v>
       </c>
       <c r="R27" t="n">
-        <v>7040172</v>
+        <v>7040210</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3491,9 +3503,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,22 +3535,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122234176</v>
+        <v>122232932</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3536,42 +3563,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563102</v>
+        <v>562795</v>
       </c>
       <c r="R28" t="n">
-        <v>7040234</v>
+        <v>7040090</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3598,24 +3620,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3630,22 +3637,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122233217</v>
+        <v>122234052</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3658,34 +3665,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562922</v>
+        <v>563109</v>
       </c>
       <c r="R29" t="n">
-        <v>7040240</v>
+        <v>7040194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3717,7 +3729,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,7 +3739,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,7 +3771,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122234125</v>
+        <v>122234176</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3795,14 +3812,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563092</v>
+        <v>563102</v>
       </c>
       <c r="R30" t="n">
-        <v>7040220</v>
+        <v>7040234</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3834,7 +3851,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3844,12 +3861,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran högstubbe</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3876,10 +3893,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122233647</v>
+        <v>122233994</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3892,39 +3909,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562988</v>
+        <v>563088</v>
       </c>
       <c r="R31" t="n">
-        <v>7040196</v>
+        <v>7040175</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3956,7 +3968,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3966,12 +3978,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3998,7 +4005,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122233260</v>
+        <v>122232402</v>
       </c>
       <c r="B32" t="n">
         <v>57383</v>
@@ -4032,24 +4039,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562896</v>
+        <v>562786</v>
       </c>
       <c r="R32" t="n">
-        <v>7040281</v>
+        <v>7040064</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4076,24 +4086,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4108,22 +4108,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122232469</v>
+        <v>122233217</v>
       </c>
       <c r="B33" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4136,21 +4136,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562748</v>
+        <v>562922</v>
       </c>
       <c r="R33" t="n">
-        <v>7040047</v>
+        <v>7040240</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4193,9 +4193,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,22 +4220,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122233933</v>
+        <v>122232184</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4238,42 +4248,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563089</v>
+        <v>562833</v>
       </c>
       <c r="R34" t="n">
-        <v>7040225</v>
+        <v>7040085</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4300,24 +4305,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,22 +4322,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122232932</v>
+        <v>122234038</v>
       </c>
       <c r="B35" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,37 +4350,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562795</v>
+        <v>563099</v>
       </c>
       <c r="R35" t="n">
-        <v>7040090</v>
+        <v>7040205</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4417,9 +4412,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4434,22 +4444,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122233127</v>
+        <v>122232949</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4462,34 +4472,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562875</v>
+        <v>562836</v>
       </c>
       <c r="R36" t="n">
-        <v>7040276</v>
+        <v>7040209</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4521,7 +4536,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4531,7 +4546,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4558,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122233673</v>
+        <v>122233260</v>
       </c>
       <c r="B37" t="n">
-        <v>79773</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,41 +4590,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562986</v>
+        <v>562896</v>
       </c>
       <c r="R37" t="n">
-        <v>7040156</v>
+        <v>7040281</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4631,9 +4656,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,19 +4688,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122232285</v>
+        <v>122232270</v>
       </c>
       <c r="B38" t="n">
         <v>79737</v>
@@ -4700,10 +4740,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562818</v>
+        <v>562828</v>
       </c>
       <c r="R38" t="n">
-        <v>7040065</v>
+        <v>7040062</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4762,10 +4802,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122234000</v>
+        <v>122232285</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4778,42 +4818,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563097</v>
+        <v>562818</v>
       </c>
       <c r="R39" t="n">
-        <v>7040210</v>
+        <v>7040065</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4840,24 +4875,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4872,22 +4892,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122234194</v>
+        <v>122233127</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,34 +4920,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563154</v>
+        <v>562875</v>
       </c>
       <c r="R40" t="n">
-        <v>7040221</v>
+        <v>7040276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4979,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4989,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4984,22 +5004,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234052</v>
+        <v>122233997</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5012,42 +5032,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563109</v>
+        <v>563095</v>
       </c>
       <c r="R41" t="n">
-        <v>7040194</v>
+        <v>7040157</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5074,24 +5089,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431528</v>
+        <v>122431459</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,34 +5357,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563173</v>
+        <v>563214</v>
       </c>
       <c r="R44" t="n">
-        <v>7040184</v>
+        <v>7040130</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5417,6 +5422,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5443,10 +5453,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431113</v>
+        <v>122431232</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,39 +5469,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562981</v>
+        <v>563034</v>
       </c>
       <c r="R45" t="n">
-        <v>7040158</v>
+        <v>7040085</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5524,11 +5529,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5558,7 +5558,7 @@
         <v>122431200</v>
       </c>
       <c r="B46" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431459</v>
+        <v>122431003</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5673,39 +5673,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563214</v>
+        <v>562919</v>
       </c>
       <c r="R47" t="n">
-        <v>7040130</v>
+        <v>7040173</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5738,11 +5733,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5769,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431232</v>
+        <v>122431113</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5785,34 +5775,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563034</v>
+        <v>562981</v>
       </c>
       <c r="R48" t="n">
-        <v>7040085</v>
+        <v>7040158</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5845,6 +5840,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,10 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431003</v>
+        <v>122431528</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5887,34 +5887,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562919</v>
+        <v>563173</v>
       </c>
       <c r="R49" t="n">
-        <v>7040173</v>
+        <v>7040184</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122233933</v>
+        <v>122232184</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563089</v>
+        <v>562833</v>
       </c>
       <c r="R11" t="n">
-        <v>7040225</v>
+        <v>7040085</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,24 +1666,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122233345</v>
+        <v>122232932</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,42 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562904</v>
+        <v>562795</v>
       </c>
       <c r="R12" t="n">
-        <v>7040280</v>
+        <v>7040090</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1793,24 +1768,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122234125</v>
+        <v>122232469</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,42 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563092</v>
+        <v>562748</v>
       </c>
       <c r="R13" t="n">
-        <v>7040220</v>
+        <v>7040047</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,24 +1870,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,12 +1887,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2061,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122234194</v>
+        <v>122233350</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,31 +2017,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563154</v>
+        <v>562930</v>
       </c>
       <c r="R15" t="n">
         <v>7040221</v>
@@ -2136,7 +2081,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2091,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233625</v>
+        <v>122233647</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,37 +2139,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562978</v>
+        <v>562988</v>
       </c>
       <c r="R16" t="n">
-        <v>7040170</v>
+        <v>7040196</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2246,9 +2201,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,19 +2233,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233647</v>
+        <v>122233933</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2320,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562988</v>
+        <v>563089</v>
       </c>
       <c r="R17" t="n">
-        <v>7040196</v>
+        <v>7040225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2325,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,12 +2335,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,19 +2355,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122233350</v>
+        <v>122234000</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2438,14 +2408,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562930</v>
+        <v>563097</v>
       </c>
       <c r="R18" t="n">
-        <v>7040221</v>
+        <v>7040210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,12 +2457,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,22 +2477,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122232469</v>
+        <v>122232495</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,7 +2532,7 @@
         <v>562748</v>
       </c>
       <c r="R19" t="n">
-        <v>7040047</v>
+        <v>7040046</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2621,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122232495</v>
+        <v>122233217</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,13 +2631,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562748</v>
+        <v>562922</v>
       </c>
       <c r="R20" t="n">
-        <v>7040046</v>
+        <v>7040240</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2694,9 +2664,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,12 +2691,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2845,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122234283</v>
+        <v>122234103</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2881,19 +2861,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563202</v>
+        <v>563089</v>
       </c>
       <c r="R22" t="n">
-        <v>7040231</v>
+        <v>7040216</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,12 +2915,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,19 +2935,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122234058</v>
+        <v>122234038</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3003,7 +2983,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3012,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563095</v>
+        <v>563099</v>
       </c>
       <c r="R23" t="n">
-        <v>7040206</v>
+        <v>7040205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3089,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234359</v>
+        <v>122234125</v>
       </c>
       <c r="B24" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,34 +3085,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563205</v>
+        <v>563092</v>
       </c>
       <c r="R24" t="n">
-        <v>7040240</v>
+        <v>7040220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3149,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3174,7 +3159,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,22 +3179,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122233673</v>
+        <v>122234058</v>
       </c>
       <c r="B25" t="n">
-        <v>79773</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3213,41 +3203,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562986</v>
+        <v>563095</v>
       </c>
       <c r="R25" t="n">
-        <v>7040156</v>
+        <v>7040206</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3274,9 +3269,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,19 +3301,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234103</v>
+        <v>122234176</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3339,19 +3349,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563089</v>
+        <v>563102</v>
       </c>
       <c r="R26" t="n">
-        <v>7040216</v>
+        <v>7040234</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,7 +3393,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3403,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3425,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122234000</v>
+        <v>122232285</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3441,42 +3451,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563097</v>
+        <v>562818</v>
       </c>
       <c r="R27" t="n">
-        <v>7040210</v>
+        <v>7040065</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,24 +3508,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,22 +3525,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122232932</v>
+        <v>122233260</v>
       </c>
       <c r="B28" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,37 +3553,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562795</v>
+        <v>562896</v>
       </c>
       <c r="R28" t="n">
-        <v>7040090</v>
+        <v>7040281</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3620,9 +3615,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,12 +3647,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3771,10 +3781,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122234176</v>
+        <v>122233673</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>79773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,46 +3793,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563102</v>
+        <v>562986</v>
       </c>
       <c r="R30" t="n">
-        <v>7040234</v>
+        <v>7040156</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3849,24 +3854,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,22 +3871,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122233994</v>
+        <v>122232270</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3909,21 +3899,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3933,13 +3923,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563088</v>
+        <v>562828</v>
       </c>
       <c r="R31" t="n">
-        <v>7040175</v>
+        <v>7040062</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,19 +3956,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,12 +3973,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4120,10 +4100,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233217</v>
+        <v>122233345</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4136,34 +4116,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562922</v>
+        <v>562904</v>
       </c>
       <c r="R33" t="n">
-        <v>7040240</v>
+        <v>7040280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4195,7 +4180,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4205,7 +4190,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4220,22 +4210,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122232184</v>
+        <v>122232949</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4248,37 +4238,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562833</v>
+        <v>562836</v>
       </c>
       <c r="R34" t="n">
-        <v>7040085</v>
+        <v>7040209</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,9 +4300,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,19 +4332,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234038</v>
+        <v>122234283</v>
       </c>
       <c r="B35" t="n">
         <v>57383</v>
@@ -4370,7 +4380,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4379,10 +4389,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563099</v>
+        <v>563202</v>
       </c>
       <c r="R35" t="n">
-        <v>7040205</v>
+        <v>7040231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4414,7 +4424,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4424,12 +4434,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,22 +4454,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122232949</v>
+        <v>122234359</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4472,39 +4482,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562836</v>
+        <v>563205</v>
       </c>
       <c r="R36" t="n">
-        <v>7040209</v>
+        <v>7040240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4536,7 +4541,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4546,12 +4551,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4566,22 +4566,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122233260</v>
+        <v>122233127</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,39 +4594,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562896</v>
+        <v>562875</v>
       </c>
       <c r="R37" t="n">
-        <v>7040281</v>
+        <v>7040276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4658,7 +4653,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4668,12 +4663,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4700,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122232270</v>
+        <v>122233997</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4716,21 +4706,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4740,10 +4730,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562828</v>
+        <v>563095</v>
       </c>
       <c r="R38" t="n">
-        <v>7040062</v>
+        <v>7040157</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4802,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122232285</v>
+        <v>122233994</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4818,21 +4808,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4842,13 +4832,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562818</v>
+        <v>563088</v>
       </c>
       <c r="R39" t="n">
-        <v>7040065</v>
+        <v>7040175</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,9 +4865,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4892,19 +4892,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233127</v>
+        <v>122233625</v>
       </c>
       <c r="B40" t="n">
         <v>79737</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562875</v>
+        <v>562978</v>
       </c>
       <c r="R40" t="n">
-        <v>7040276</v>
+        <v>7040170</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4977,19 +4977,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5004,19 +4994,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122233997</v>
+        <v>122234194</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -5052,17 +5042,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563095</v>
+        <v>563154</v>
       </c>
       <c r="R41" t="n">
-        <v>7040157</v>
+        <v>7040221</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5089,9 +5079,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,12 +5106,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431459</v>
+        <v>122431113</v>
       </c>
       <c r="B44" t="n">
         <v>57383</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563214</v>
+        <v>562981</v>
       </c>
       <c r="R44" t="n">
-        <v>7040130</v>
+        <v>7040158</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431232</v>
+        <v>122431200</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563034</v>
+        <v>563033</v>
       </c>
       <c r="R45" t="n">
         <v>7040085</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431200</v>
+        <v>122431528</v>
       </c>
       <c r="B46" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5571,34 +5571,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563033</v>
+        <v>563173</v>
       </c>
       <c r="R46" t="n">
-        <v>7040085</v>
+        <v>7040184</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431003</v>
+        <v>122431459</v>
       </c>
       <c r="B47" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5673,34 +5673,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562919</v>
+        <v>563214</v>
       </c>
       <c r="R47" t="n">
-        <v>7040173</v>
+        <v>7040130</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5733,6 +5738,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,10 +5769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431113</v>
+        <v>122431003</v>
       </c>
       <c r="B48" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,39 +5785,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562981</v>
+        <v>562919</v>
       </c>
       <c r="R48" t="n">
-        <v>7040158</v>
+        <v>7040173</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5840,11 +5845,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,7 +5871,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431528</v>
+        <v>122431232</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5907,14 +5907,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563173</v>
+        <v>563034</v>
       </c>
       <c r="R49" t="n">
-        <v>7040184</v>
+        <v>7040085</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -5121,7 +5121,7 @@
         <v>122233875</v>
       </c>
       <c r="B42" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>122431113</v>
       </c>
       <c r="B44" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>122431200</v>
       </c>
       <c r="B45" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431528</v>
+        <v>122431003</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5571,34 +5571,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563173</v>
+        <v>562919</v>
       </c>
       <c r="R46" t="n">
-        <v>7040184</v>
+        <v>7040173</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5660,7 +5660,7 @@
         <v>122431459</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431003</v>
+        <v>122431232</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5785,21 +5785,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562919</v>
+        <v>563034</v>
       </c>
       <c r="R48" t="n">
-        <v>7040173</v>
+        <v>7040085</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431232</v>
+        <v>122431528</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5907,14 +5907,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563034</v>
+        <v>563173</v>
       </c>
       <c r="R49" t="n">
-        <v>7040085</v>
+        <v>7040184</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431459</v>
+        <v>122431232</v>
       </c>
       <c r="B47" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5673,39 +5673,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563214</v>
+        <v>563034</v>
       </c>
       <c r="R47" t="n">
-        <v>7040130</v>
+        <v>7040085</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5738,11 +5733,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5769,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431232</v>
+        <v>122431459</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5785,34 +5775,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563034</v>
+        <v>563214</v>
       </c>
       <c r="R48" t="n">
-        <v>7040085</v>
+        <v>7040130</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5845,6 +5840,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -5242,7 +5242,7 @@
         <v>122356076</v>
       </c>
       <c r="B43" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431113</v>
+        <v>122431003</v>
       </c>
       <c r="B44" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,39 +5357,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562981</v>
+        <v>562919</v>
       </c>
       <c r="R44" t="n">
-        <v>7040158</v>
+        <v>7040173</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5422,11 +5417,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5446,7 @@
         <v>122431200</v>
       </c>
       <c r="B45" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5555,10 +5545,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431003</v>
+        <v>122431232</v>
       </c>
       <c r="B46" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5571,21 +5561,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5595,10 +5585,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562919</v>
+        <v>563034</v>
       </c>
       <c r="R46" t="n">
-        <v>7040173</v>
+        <v>7040085</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5657,10 +5647,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431232</v>
+        <v>122431459</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5673,34 +5663,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563034</v>
+        <v>563214</v>
       </c>
       <c r="R47" t="n">
-        <v>7040085</v>
+        <v>7040130</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5733,6 +5728,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,7 +5759,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431459</v>
+        <v>122431113</v>
       </c>
       <c r="B48" t="n">
         <v>57384</v>
@@ -5800,14 +5800,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563214</v>
+        <v>562981</v>
       </c>
       <c r="R48" t="n">
-        <v>7040130</v>
+        <v>7040158</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5874,7 +5874,7 @@
         <v>122431528</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -5341,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431003</v>
+        <v>122431459</v>
       </c>
       <c r="B44" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,34 +5357,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562919</v>
+        <v>563214</v>
       </c>
       <c r="R44" t="n">
-        <v>7040173</v>
+        <v>7040130</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5417,6 +5422,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5443,10 +5453,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431200</v>
+        <v>122431113</v>
       </c>
       <c r="B45" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5459,34 +5469,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563033</v>
+        <v>562981</v>
       </c>
       <c r="R45" t="n">
-        <v>7040085</v>
+        <v>7040158</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5519,6 +5534,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,7 +5565,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431232</v>
+        <v>122431528</v>
       </c>
       <c r="B46" t="n">
         <v>78660</v>
@@ -5581,14 +5601,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563034</v>
+        <v>563173</v>
       </c>
       <c r="R46" t="n">
-        <v>7040085</v>
+        <v>7040184</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5647,10 +5667,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431459</v>
+        <v>122431200</v>
       </c>
       <c r="B47" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5663,39 +5683,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563214</v>
+        <v>563033</v>
       </c>
       <c r="R47" t="n">
-        <v>7040130</v>
+        <v>7040085</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5728,11 +5743,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,10 +5769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431113</v>
+        <v>122431003</v>
       </c>
       <c r="B48" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5775,39 +5785,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562981</v>
+        <v>562919</v>
       </c>
       <c r="R48" t="n">
-        <v>7040158</v>
+        <v>7040173</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5840,11 +5845,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,7 +5871,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431528</v>
+        <v>122431232</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5907,14 +5907,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563173</v>
+        <v>563034</v>
       </c>
       <c r="R49" t="n">
-        <v>7040184</v>
+        <v>7040085</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111630866</v>
+        <v>111630882</v>
       </c>
       <c r="B2" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563220</v>
+        <v>562879</v>
       </c>
       <c r="R2" t="n">
-        <v>7040220</v>
+        <v>7040298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111630862</v>
+        <v>122233875</v>
       </c>
       <c r="B3" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562923</v>
+        <v>563056</v>
       </c>
       <c r="R3" t="n">
-        <v>7040174</v>
+        <v>7040119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,33 +854,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111630857</v>
+        <v>111630862</v>
       </c>
       <c r="B4" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563003</v>
+        <v>562923</v>
       </c>
       <c r="R4" t="n">
-        <v>7040107</v>
+        <v>7040174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +988,7 @@
         <v>111630864</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111630860</v>
+        <v>122232469</v>
       </c>
       <c r="B6" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1093,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562934</v>
+        <v>562748</v>
       </c>
       <c r="R6" t="n">
-        <v>7040168</v>
+        <v>7040047</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1167,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111630870</v>
+        <v>111630866</v>
       </c>
       <c r="B7" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1190,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563075</v>
+        <v>563220</v>
       </c>
       <c r="R7" t="n">
-        <v>7040090</v>
+        <v>7040220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1279,7 @@
         <v>111630868</v>
       </c>
       <c r="B8" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,15 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111630858</v>
+        <v>122232932</v>
       </c>
       <c r="B9" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1384,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562934</v>
+        <v>562795</v>
       </c>
       <c r="R9" t="n">
-        <v>7040168</v>
+        <v>7040090</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1438,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,27 +1458,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111630872</v>
+        <v>122234359</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1481,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563060</v>
+        <v>563205</v>
       </c>
       <c r="R10" t="n">
-        <v>7040084</v>
+        <v>7040240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1535,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,27 +1565,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122232184</v>
+        <v>111630858</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,37 +1588,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562934</v>
       </c>
       <c r="R11" t="n">
-        <v>7040085</v>
+        <v>7040168</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,27 +1662,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122232932</v>
+        <v>122233646</v>
       </c>
       <c r="B12" t="n">
-        <v>82443</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1685,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562795</v>
+        <v>562989</v>
       </c>
       <c r="R12" t="n">
-        <v>7040090</v>
+        <v>7040172</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,37 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122232469</v>
+        <v>122232184</v>
       </c>
       <c r="B13" t="n">
-        <v>90833</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562748</v>
+        <v>562833</v>
       </c>
       <c r="R13" t="n">
-        <v>7040047</v>
+        <v>7040085</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,37 +1868,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122233646</v>
+        <v>122233217</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1903,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562989</v>
+        <v>562922</v>
       </c>
       <c r="R14" t="n">
-        <v>7040172</v>
+        <v>7040240</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1972,9 +1936,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,67 +1963,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122233350</v>
+        <v>122233994</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562930</v>
+        <v>563088</v>
       </c>
       <c r="R15" t="n">
-        <v>7040221</v>
+        <v>7040175</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2045,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2091,12 +2055,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,58 +2082,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122233647</v>
+        <v>122233997</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562988</v>
+        <v>563095</v>
       </c>
       <c r="R16" t="n">
-        <v>7040196</v>
+        <v>7040157</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2201,24 +2150,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,67 +2167,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122233933</v>
+        <v>122234194</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563089</v>
+        <v>563154</v>
       </c>
       <c r="R17" t="n">
-        <v>7040225</v>
+        <v>7040221</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2249,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2335,12 +2259,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på stående gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,67 +2274,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122234000</v>
+        <v>122234448</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563097</v>
+        <v>563179</v>
       </c>
       <c r="R18" t="n">
-        <v>7040210</v>
+        <v>7040282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2356,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,12 +2366,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,49 +2381,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122232495</v>
+        <v>122431232</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562748</v>
+        <v>563034</v>
       </c>
       <c r="R19" t="n">
-        <v>7040046</v>
+        <v>7040085</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2559,12 +2458,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,19 +2490,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122233217</v>
+        <v>122431528</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2627,17 +2521,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562922</v>
+        <v>563173</v>
       </c>
       <c r="R20" t="n">
-        <v>7040240</v>
+        <v>7040184</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2661,22 +2555,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,27 +2575,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122233750</v>
+        <v>111630870</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,39 +2598,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563040</v>
+        <v>563075</v>
       </c>
       <c r="R21" t="n">
-        <v>7040180</v>
+        <v>7040090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,27 +2652,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,27 +2672,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122234103</v>
+        <v>111630860</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,39 +2695,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563089</v>
+        <v>562934</v>
       </c>
       <c r="R22" t="n">
-        <v>7040216</v>
+        <v>7040168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,27 +2749,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,27 +2769,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122234038</v>
+        <v>111630872</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563099</v>
+        <v>563060</v>
       </c>
       <c r="R23" t="n">
-        <v>7040205</v>
+        <v>7040085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,27 +2846,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,27 +2866,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122234125</v>
+        <v>122232270</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,42 +2889,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563092</v>
+        <v>562828</v>
       </c>
       <c r="R24" t="n">
-        <v>7040220</v>
+        <v>7040062</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3147,24 +2946,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,27 +2963,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122234058</v>
+        <v>122232285</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3207,42 +2986,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563095</v>
+        <v>562818</v>
       </c>
       <c r="R25" t="n">
-        <v>7040206</v>
+        <v>7040065</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3269,24 +3043,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3301,27 +3060,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122234176</v>
+        <v>122232495</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,42 +3083,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563102</v>
+        <v>562748</v>
       </c>
       <c r="R26" t="n">
-        <v>7040234</v>
+        <v>7040046</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3391,24 +3140,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,27 +3157,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122232285</v>
+        <v>122232722</v>
       </c>
       <c r="B27" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,10 +3204,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562818</v>
+        <v>562722</v>
       </c>
       <c r="R27" t="n">
-        <v>7040065</v>
+        <v>7040069</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3537,15 +3266,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122233260</v>
+        <v>122233127</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3553,39 +3277,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562896</v>
+        <v>562875</v>
       </c>
       <c r="R28" t="n">
-        <v>7040281</v>
+        <v>7040276</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3336,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,12 +3346,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,15 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122234052</v>
+        <v>122233625</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,42 +3384,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563109</v>
+        <v>562978</v>
       </c>
       <c r="R29" t="n">
-        <v>7040194</v>
+        <v>7040170</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3737,24 +3441,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,49 +3458,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122233673</v>
+        <v>122356076</v>
       </c>
       <c r="B30" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3821,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562986</v>
+        <v>563071</v>
       </c>
       <c r="R30" t="n">
-        <v>7040156</v>
+        <v>7040224</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3851,12 +3535,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,15 +3567,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232270</v>
+        <v>122431003</v>
       </c>
       <c r="B31" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3923,10 +3602,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562828</v>
+        <v>562919</v>
       </c>
       <c r="R31" t="n">
-        <v>7040062</v>
+        <v>7040173</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3953,12 +3632,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3985,15 +3664,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122232402</v>
+        <v>122431344</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,42 +3675,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562786</v>
+        <v>563165</v>
       </c>
       <c r="R32" t="n">
-        <v>7040064</v>
+        <v>7040116</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4063,17 +3729,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4100,58 +3761,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122233345</v>
+        <v>122233673</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562904</v>
+        <v>562986</v>
       </c>
       <c r="R33" t="n">
-        <v>7040280</v>
+        <v>7040156</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4178,24 +3829,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,27 +3846,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122232949</v>
+        <v>122232402</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,24 +3887,27 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562836</v>
+        <v>562786</v>
       </c>
       <c r="R34" t="n">
-        <v>7040209</v>
+        <v>7040064</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4300,24 +3934,14 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,27 +3956,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122234283</v>
+        <v>122232949</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,19 +3999,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563202</v>
+        <v>562836</v>
       </c>
       <c r="R35" t="n">
-        <v>7040231</v>
+        <v>7040209</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,7 +4043,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4434,12 +4053,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4454,27 +4073,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122234359</v>
+        <v>122233260</v>
       </c>
       <c r="B36" t="n">
-        <v>82443</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,34 +4096,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563205</v>
+        <v>562896</v>
       </c>
       <c r="R36" t="n">
-        <v>7040240</v>
+        <v>7040281</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,7 +4160,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4551,7 +4170,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4566,27 +4190,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122233127</v>
+        <v>122233345</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4594,34 +4213,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562875</v>
+        <v>562904</v>
       </c>
       <c r="R37" t="n">
-        <v>7040276</v>
+        <v>7040280</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4653,7 +4277,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4663,7 +4287,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,15 +4319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122233997</v>
+        <v>122233350</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,37 +4330,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563095</v>
+        <v>562930</v>
       </c>
       <c r="R38" t="n">
-        <v>7040157</v>
+        <v>7040221</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4763,9 +4392,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,27 +4424,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122233994</v>
+        <v>122233647</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4808,34 +4447,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563088</v>
+        <v>562988</v>
       </c>
       <c r="R39" t="n">
-        <v>7040175</v>
+        <v>7040196</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4867,7 +4511,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4877,7 +4521,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4904,15 +4553,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122233625</v>
+        <v>122233750</v>
       </c>
       <c r="B40" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,37 +4564,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562978</v>
+        <v>563040</v>
       </c>
       <c r="R40" t="n">
-        <v>7040170</v>
+        <v>7040180</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4977,9 +4626,24 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,27 +4658,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122234194</v>
+        <v>122233933</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,34 +4681,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563154</v>
+        <v>563089</v>
       </c>
       <c r="R41" t="n">
-        <v>7040221</v>
+        <v>7040225</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5081,7 +4745,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5091,7 +4755,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på stående gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,27 +4775,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122233875</v>
+        <v>122234000</v>
       </c>
       <c r="B42" t="n">
-        <v>79604</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5134,40 +4798,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563056</v>
+        <v>563097</v>
       </c>
       <c r="R42" t="n">
-        <v>7040119</v>
+        <v>7040210</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5194,60 +4860,54 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122356076</v>
+        <v>122234038</v>
       </c>
       <c r="B43" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5255,37 +4915,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563071</v>
+        <v>563099</v>
       </c>
       <c r="R43" t="n">
-        <v>7040224</v>
+        <v>7040205</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5309,12 +4974,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5329,27 +5009,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122431528</v>
+        <v>122234052</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,37 +5032,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563173</v>
+        <v>563109</v>
       </c>
       <c r="R44" t="n">
-        <v>7040184</v>
+        <v>7040194</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5411,12 +5091,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5431,27 +5126,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122431003</v>
+        <v>122234058</v>
       </c>
       <c r="B45" t="n">
-        <v>79843</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5459,37 +5149,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562919</v>
+        <v>563095</v>
       </c>
       <c r="R45" t="n">
-        <v>7040173</v>
+        <v>7040206</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,12 +5208,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5533,27 +5243,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122431113</v>
+        <v>122234103</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5590,13 +5295,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562981</v>
+        <v>563089</v>
       </c>
       <c r="R46" t="n">
-        <v>7040158</v>
+        <v>7040216</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,17 +5325,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,27 +5360,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122431459</v>
+        <v>122234125</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5693,22 +5403,22 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563214</v>
+        <v>563092</v>
       </c>
       <c r="R47" t="n">
-        <v>7040130</v>
+        <v>7040220</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5732,17 +5442,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på gran högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5757,27 +5477,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122431232</v>
+        <v>122234176</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5785,37 +5500,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563034</v>
+        <v>563102</v>
       </c>
       <c r="R48" t="n">
-        <v>7040085</v>
+        <v>7040234</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5839,12 +5559,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,27 +5594,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122431200</v>
+        <v>122234283</v>
       </c>
       <c r="B49" t="n">
-        <v>90958</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5887,37 +5617,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563033</v>
+        <v>563202</v>
       </c>
       <c r="R49" t="n">
-        <v>7040085</v>
+        <v>7040231</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5941,12 +5676,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5961,15 +5711,427 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122431113</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>562981</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7040158</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122431459</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>563214</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7040130</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122232618</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>562689</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7040030</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>111630857</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Håsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>563003</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7040107</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61326-2024 artfynd.xlsx
+++ b/artfynd/A 61326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232469</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630866</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233646</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232184</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1972,6 +2037,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233994</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233997</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2283,6 +2363,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234194</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2390,6 +2475,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234448</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2487,6 +2577,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431232</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2584,6 +2679,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431528</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2681,6 +2781,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2778,6 +2883,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630860</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2875,6 +2985,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630872</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2972,6 +3087,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232270</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232285</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3166,6 +3291,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232495</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3263,6 +3393,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232722</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3370,6 +3505,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233127</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3467,6 +3607,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233625</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3564,6 +3709,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356076</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3661,6 +3811,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431003</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3758,6 +3913,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431344</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3855,6 +4015,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233673</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3965,6 +4130,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232402</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4082,6 +4252,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232949</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4199,6 +4374,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233260</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4316,6 +4496,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233345</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4433,6 +4618,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233350</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4550,6 +4740,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233647</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4667,6 +4862,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233750</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4784,6 +4984,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233933</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4901,6 +5106,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234000</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5018,6 +5228,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5135,6 +5350,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234052</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5252,6 +5472,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234058</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5369,6 +5594,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234103</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5486,6 +5716,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234125</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5603,6 +5838,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234176</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5720,6 +5960,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234283</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5827,6 +6072,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431113</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5934,6 +6184,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122431459</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6035,6 +6290,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122232618</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6132,8 +6392,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>